--- a/question-bank/CSS_Question_Bank.xlsx
+++ b/question-bank/CSS_Question_Bank.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q01-style-a-profile-card.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q01-style-a-profile-card.html</t>
   </si>
   <si>
     <t xml:space="preserve">2. Format Article Typography</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Use rem units for font sizes. Keep body text left aligned.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q02-format-article-typography.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q02-format-article-typography.html</t>
   </si>
   <si>
     <t xml:space="preserve">3. Create a Color Badge Set</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Badge text must remain readable with sufficient contrast.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q03-create-a-color-badge-set.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q03-create-a-color-badge-set.html</t>
   </si>
   <si>
     <t xml:space="preserve">4. Apply the Box Model</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">Cards must have equal width and visible borders.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q04-apply-the-box-model.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q04-apply-the-box-model.html</t>
   </si>
   <si>
     <t xml:space="preserve">5. Style a Login Form</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">Do not use JavaScript. Keep fields full width inside the form.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q05-style-a-login-form.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q05-style-a-login-form.html</t>
   </si>
   <si>
     <t xml:space="preserve">6. Add Background Effects</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">The heading must remain visible over the background.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q06-add-background-effects.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q06-add-background-effects.html</t>
   </si>
   <si>
     <t xml:space="preserve">7. Build a Navigation Bar</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">Nav links must have consistent spacing and no underline by default.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q07-build-a-navigation-bar.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q07-build-a-navigation-bar.html</t>
   </si>
   <si>
     <t xml:space="preserve">8. Design a Product Tile</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">Avoid using !important.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q08-design-a-product-tile.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q08-design-a-product-tile.html</t>
   </si>
   <si>
     <t xml:space="preserve">9. Normalize Page Spacing</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Do not remove focus outlines.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q09-normalize-page-spacing.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q09-normalize-page-spacing.html</t>
   </si>
   <si>
     <t xml:space="preserve">10. Create Text Utility Classes</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">Each utility class must do one job only.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q10-create-text-utility-classes.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q10-create-text-utility-classes.html</t>
   </si>
   <si>
     <t xml:space="preserve">CSS Layout Systems</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q11-flex-navbar-alignment.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q11-flex-navbar-alignment.html</t>
   </si>
   <si>
     <t xml:space="preserve">2. Responsive Card Row</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">Cards must not overlap when the viewport is narrow.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q12-responsive-card-row.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q12-responsive-card-row.html</t>
   </si>
   <si>
     <t xml:space="preserve">3. Two Column Portfolio Layout</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">At desktop width, text must appear before image.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q13-two-column-portfolio-layout.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q13-two-column-portfolio-layout.html</t>
   </si>
   <si>
     <t xml:space="preserve">4. Analytics Dashboard Grid</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">Sidebar must keep a fixed width on desktop.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q14-analytics-dashboard-grid.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q14-analytics-dashboard-grid.html</t>
   </si>
   <si>
     <t xml:space="preserve">5. Absolute Badge Position</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">Badge must stay inside the card boundary.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q15-absolute-badge-position.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q15-absolute-badge-position.html</t>
   </si>
   <si>
     <t xml:space="preserve">6. Sticky Section Header</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">Toolbar must not cover the first row.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q16-sticky-section-header.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q16-sticky-section-header.html</t>
   </si>
   <si>
     <t xml:space="preserve">7. Fixed Support Button</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">Button must remain visible above page content.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q17-fixed-support-button.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q17-fixed-support-button.html</t>
   </si>
   <si>
     <t xml:space="preserve">8. Layered Modal Overlay</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">Modal must appear above overlay.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q18-layered-modal-overlay.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q18-layered-modal-overlay.html</t>
   </si>
   <si>
     <t xml:space="preserve">9. Grid Gallery Layout</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">Gallery items must keep equal gaps.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q19-grid-gallery-layout.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q19-grid-gallery-layout.html</t>
   </si>
   <si>
     <t xml:space="preserve">10. Flex Form Controls</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">Input should take remaining width.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q20-flex-form-controls.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q20-flex-form-controls.html</t>
   </si>
   <si>
     <t xml:space="preserve">Responsive Web Design</t>
@@ -441,7 +441,7 @@
 HTML: Provided responsive component markup</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q21-mobile-first-navbar.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q21-mobile-first-navbar.html</t>
   </si>
   <si>
     <t xml:space="preserve">2. Responsive Card Grid</t>
@@ -459,7 +459,7 @@
     <t xml:space="preserve">Must start as one column on small screens.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q22-responsive-card-grid.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q22-responsive-card-grid.html</t>
   </si>
   <si>
     <t xml:space="preserve">3. Fluid Hero Sizing</t>
@@ -477,7 +477,7 @@
     <t xml:space="preserve">Do not use fixed pixel widths for the main container.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q23-fluid-hero-sizing.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q23-fluid-hero-sizing.html</t>
   </si>
   <si>
     <t xml:space="preserve">4. Responsive Form Layout</t>
@@ -495,7 +495,7 @@
     <t xml:space="preserve">Labels must stay above their fields.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q24-responsive-form-layout.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q24-responsive-form-layout.html</t>
   </si>
   <si>
     <t xml:space="preserve">5. Adaptive Dashboard Panels</t>
@@ -513,7 +513,7 @@
     <t xml:space="preserve">Widgets must preserve readable spacing.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q25-adaptive-dashboard-panels.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q25-adaptive-dashboard-panels.html</t>
   </si>
   <si>
     <t xml:space="preserve">6. Responsive Image Treatment</t>
@@ -531,7 +531,7 @@
     <t xml:space="preserve">Images must not overflow their containers.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q26-responsive-image-treatment.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q26-responsive-image-treatment.html</t>
   </si>
   <si>
     <t xml:space="preserve">7. Viewport Based Split Section</t>
@@ -549,7 +549,7 @@
     <t xml:space="preserve">Mobile content must not be clipped.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q27-viewport-based-split-section.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q27-viewport-based-split-section.html</t>
   </si>
   <si>
     <t xml:space="preserve">8. Responsive Table Alternative</t>
@@ -567,7 +567,7 @@
     <t xml:space="preserve">Each mobile row must show label and value.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q28-responsive-table-alternative.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q28-responsive-table-alternative.html</t>
   </si>
   <si>
     <t xml:space="preserve">9. Scalable Spacing System</t>
@@ -585,7 +585,7 @@
     <t xml:space="preserve">Avoid hardcoding repeated pixel spacing.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q29-scalable-spacing-system.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q29-scalable-spacing-system.html</t>
   </si>
   <si>
     <t xml:space="preserve">10. Accessible Responsive Footer</t>
@@ -603,7 +603,7 @@
     <t xml:space="preserve">Link tap targets must be at least 44px high on mobile.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q30-accessible-responsive-footer.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q30-accessible-responsive-footer.html</t>
   </si>
   <si>
     <t xml:space="preserve">Tailwind CSS</t>
@@ -627,7 +627,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-profile-card"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q31-tailwind-profile-card.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q31-tailwind-profile-card.html</t>
   </si>
   <si>
     <t xml:space="preserve">2. Tailwind Responsive Navbar</t>
@@ -648,7 +648,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-responsive-navbar"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q32-tailwind-responsive-navbar.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q32-tailwind-responsive-navbar.html</t>
   </si>
   <si>
     <t xml:space="preserve">3. Tailwind Course Grid</t>
@@ -669,7 +669,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-course-grid"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q33-tailwind-course-grid.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q33-tailwind-course-grid.html</t>
   </si>
   <si>
     <t xml:space="preserve">4. Tailwind Button States</t>
@@ -690,7 +690,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-button-states"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q34-tailwind-button-states.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q34-tailwind-button-states.html</t>
   </si>
   <si>
     <t xml:space="preserve">5. Tailwind Form Panel</t>
@@ -711,7 +711,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-form-panel"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q35-tailwind-form-panel.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q35-tailwind-form-panel.html</t>
   </si>
   <si>
     <t xml:space="preserve">6. Tailwind Sidebar Layout</t>
@@ -732,7 +732,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-sidebar-layout"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q36-tailwind-sidebar-layout.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q36-tailwind-sidebar-layout.html</t>
   </si>
   <si>
     <t xml:space="preserve">7. Tailwind Theme Color Usage</t>
@@ -753,7 +753,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-theme-color-usage"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q37-tailwind-theme-color-usage.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q37-tailwind-theme-color-usage.html</t>
   </si>
   <si>
     <t xml:space="preserve">8. Tailwind Spacing System</t>
@@ -774,7 +774,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-spacing-system"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q38-tailwind-spacing-system.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q38-tailwind-spacing-system.html</t>
   </si>
   <si>
     <t xml:space="preserve">9. Tailwind Dashboard Widgets</t>
@@ -795,7 +795,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-dashboard-widgets"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q39-tailwind-dashboard-widgets.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q39-tailwind-dashboard-widgets.html</t>
   </si>
   <si>
     <t xml:space="preserve">10. Tailwind Production Component</t>
@@ -816,7 +816,7 @@
     <t xml:space="preserve">&lt;div class="challenge tailwind-production-component"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q40-tailwind-production-component.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q40-tailwind-production-component.html</t>
   </si>
   <si>
     <t xml:space="preserve">UI Design Concepts</t>
@@ -841,7 +841,7 @@
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q41-hoverable-dashboard-card.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q41-hoverable-dashboard-card.html</t>
   </si>
   <si>
     <t xml:space="preserve">2. Animated Submit Button</t>
@@ -859,7 +859,7 @@
     <t xml:space="preserve">Disabled state must look inactive and block pointer styling.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q42-animated-submit-button.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q42-animated-submit-button.html</t>
   </si>
   <si>
     <t xml:space="preserve">3. Skeleton Loading Card</t>
@@ -877,7 +877,7 @@
     <t xml:space="preserve">Animation should be smooth and not distract users.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q43-skeleton-loading-card.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q43-skeleton-loading-card.html</t>
   </si>
   <si>
     <t xml:space="preserve">4. Sidebar Navigation States</t>
@@ -895,7 +895,7 @@
     <t xml:space="preserve">Active state must differ from hover state.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q44-sidebar-navigation-states.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q44-sidebar-navigation-states.html</t>
   </si>
   <si>
     <t xml:space="preserve">5. Interactive Form Feedback</t>
@@ -913,7 +913,7 @@
     <t xml:space="preserve">Invalid state must not rely only on color.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q45-interactive-form-feedback.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q45-interactive-form-feedback.html</t>
   </si>
   <si>
     <t xml:space="preserve">6. Card Widget Hierarchy</t>
@@ -931,7 +931,7 @@
     <t xml:space="preserve">The metric value must be the most prominent element.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q46-card-widget-hierarchy.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q46-card-widget-hierarchy.html</t>
   </si>
   <si>
     <t xml:space="preserve">7. Fade In Content Section</t>
@@ -949,7 +949,7 @@
     <t xml:space="preserve">Animation duration must be under 500ms.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q47-fade-in-content-section.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q47-fade-in-content-section.html</t>
   </si>
   <si>
     <t xml:space="preserve">8. Accessible Tooltip Styling</t>
@@ -967,7 +967,7 @@
     <t xml:space="preserve">Tooltip must work with keyboard focus.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q48-accessible-tooltip-styling.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q48-accessible-tooltip-styling.html</t>
   </si>
   <si>
     <t xml:space="preserve">9. Interactive Modal Motion</t>
@@ -985,7 +985,7 @@
     <t xml:space="preserve">Respect reduced motion with a media query.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q49-interactive-modal-motion.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q49-interactive-modal-motion.html</t>
   </si>
   <si>
     <t xml:space="preserve">10. Empty State Panel</t>
@@ -1003,7 +1003,7 @@
     <t xml:space="preserve">The action button must remain visually prominent.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q50-empty-state-panel.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q50-empty-state-panel.html</t>
   </si>
   <si>
     <t xml:space="preserve">Production-Level Frontend Styling</t>
@@ -1027,7 +1027,7 @@
     <t xml:space="preserve">Existing component classes and semantic HTML from a React frontend</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q51-reusable-component-classes.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q51-reusable-component-classes.html</t>
   </si>
   <si>
     <t xml:space="preserve">2. Organized CSS Structure</t>
@@ -1045,7 +1045,7 @@
     <t xml:space="preserve">Keep selectors readable and avoid deep nesting.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q52-organized-css-structure.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q52-organized-css-structure.html</t>
   </si>
   <si>
     <t xml:space="preserve">3. CSS Variables Theme</t>
@@ -1063,7 +1063,7 @@
     <t xml:space="preserve">Components must use variables instead of hardcoded colors.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q53-css-variables-theme.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q53-css-variables-theme.html</t>
   </si>
   <si>
     <t xml:space="preserve">4. Accessible Contrast Fix</t>
@@ -1081,7 +1081,7 @@
     <t xml:space="preserve">Do not reduce font size to solve layout issues.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q54-accessible-contrast-fix.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q54-accessible-contrast-fix.html</t>
   </si>
   <si>
     <t xml:space="preserve">5. Production Form Component</t>
@@ -1099,7 +1099,7 @@
     <t xml:space="preserve">Error text must be visible and associated with the field visually.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q55-production-form-component.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q55-production-form-component.html</t>
   </si>
   <si>
     <t xml:space="preserve">6. Optimize CSS Asset Usage</t>
@@ -1117,7 +1117,7 @@
     <t xml:space="preserve">Do not remove required brand visuals.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q56-optimize-css-asset-usage.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q56-optimize-css-asset-usage.html</t>
   </si>
   <si>
     <t xml:space="preserve">7. Component Scoped Naming</t>
@@ -1135,7 +1135,7 @@
     <t xml:space="preserve">Class names must communicate component ownership.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q57-component-scoped-naming.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q57-component-scoped-naming.html</t>
   </si>
   <si>
     <t xml:space="preserve">8. Production Dashboard Layout</t>
@@ -1153,7 +1153,7 @@
     <t xml:space="preserve">The shell must remain usable on mobile.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q58-production-dashboard-layout.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q58-production-dashboard-layout.html</t>
   </si>
   <si>
     <t xml:space="preserve">9. Semantic UI Styling</t>
@@ -1171,7 +1171,7 @@
     <t xml:space="preserve">Do not remove outlines or hide labels.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q59-semantic-ui-styling.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q59-semantic-ui-styling.html</t>
   </si>
   <si>
     <t xml:space="preserve">10. Performance Friendly Animation</t>
@@ -1189,7 +1189,7 @@
     <t xml:space="preserve">Avoid animating width, height, top, or left.</t>
   </si>
   <si>
-    <t xml:space="preserve">https://nithya-sri-14.github.io/css-beginner/question-bank/outputs/q60-performance-friendly-animation.html</t>
+    <t xml:space="preserve">https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q60-performance-friendly-animation.html</t>
   </si>
 </sst>
 </file>

--- a/question-bank/CSS_Question_Bank.xlsx
+++ b/question-bank/CSS_Question_Bank.xlsx
@@ -10,7 +10,7 @@
     <sheet name="CSS Question Bank" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CSS Question Bank'!$A$1:$J$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CSS Question Bank'!$A$1:$J$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CSSQuestionBank" displayName="CSSQuestionBank" ref="A1:J61" headerRowCount="1">
-  <autoFilter ref="A1:J61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CSSQuestionBank" displayName="CSSQuestionBank" ref="A1:J121" headerRowCount="1">
+  <autoFilter ref="A1:J121"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Language"/>
     <tableColumn id="2" name="Level"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1104,42 +1104,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1. Flex Navbar Alignment</t>
+          <t>11. Style Heading Levels</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Use Flexbox to align logo, links, and action button in one responsive navbar row.</t>
+          <t>Write CSS for h1, h2, and h3 headings using font size, weight, color, and spacing.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>A dashboard header needs predictable horizontal alignment.</t>
+          <t>An LMS lesson page needs clear heading hierarchy.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Use justify-content and align-items on the navbar container.</t>
+          <t>Use element selectors and avoid inline styles.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Do not use floats. Keep the logo on the left and button on the right.</t>
+          <t>Each heading level must look visually distinct.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q11-flex-navbar-alignment.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q11-style-heading-levels.html</t>
         </is>
       </c>
     </row>
@@ -1156,42 +1156,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2. Responsive Card Row</t>
+          <t>12. Create Link Styles</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Arrange four feature cards with Flexbox and wrapping.</t>
+          <t>Style default, hover, focus, and visited link states for a content page.</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>A course overview page must show cards neatly across screen sizes.</t>
+          <t>A documentation page needs readable and accessible links.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Use flex-wrap and gap.</t>
+          <t>Use anchor pseudo-classes in a logical order.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Cards must not overlap when the viewport is narrow.</t>
+          <t>Do not remove keyboard focus visibility.</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q12-responsive-card-row.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q12-create-link-styles.html</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3. Two Column Portfolio Layout</t>
+          <t>13. Build Alert Boxes</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Use CSS Grid to create a profile section with content and image columns.</t>
+          <t>Create info, success, warning, and error alert styles using reusable classes.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>A personal portfolio needs a clean intro block.</t>
+          <t>A practice platform shows feedback after code submission.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Use grid-template-columns and align-items.</t>
+          <t>Use one base alert class and modifier classes.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>At desktop width, text must appear before image.</t>
+          <t>Each alert must include padding, border, and readable colors.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q13-two-column-portfolio-layout.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q13-build-alert-boxes.html</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4. Analytics Dashboard Grid</t>
+          <t>14. Use Font Families Correctly</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Build a dashboard layout with CSS Grid areas for sidebar, header, metrics, and chart.</t>
+          <t>Apply fallback font stacks for a page title, body text, and code snippet.</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>An API-driven analytics dashboard needs a repeatable page structure.</t>
+          <t>A coding lesson page needs different text styles for prose and code.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Name grid areas clearly.</t>
+          <t>Use font-family with multiple fallbacks.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Sidebar must keep a fixed width on desktop.</t>
+          <t>Code text must use a monospace stack.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q14-analytics-dashboard-grid.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q14-use-font-families-correctly.html</t>
         </is>
       </c>
     </row>
@@ -1312,42 +1312,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5. Absolute Badge Position</t>
+          <t>15. Control Element Widths</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Position a notification badge on the top-right corner of a card.</t>
+          <t>Set max-width, width, and min-height for a centered content container.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>A UI card needs a small unread-count badge.</t>
+          <t>A course article should not stretch too wide on large screens.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Set the card to relative and the badge to absolute.</t>
+          <t>Use margin auto for horizontal centering.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Badge must stay inside the card boundary.</t>
+          <t>Container width must remain responsive.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q15-absolute-badge-position.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q15-control-element-widths.html</t>
         </is>
       </c>
     </row>
@@ -1364,42 +1364,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6. Sticky Section Header</t>
+          <t>16. Add Border Variations</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Create a sticky table toolbar that stays visible while scrolling.</t>
+          <t>Create solid, dashed, and accent border styles for content blocks.</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>An LMS table of learners has many rows.</t>
+          <t>A notes page needs different callout styles.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Use position: sticky with a top offset.</t>
+          <t>Use class selectors for each border type.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Toolbar must not cover the first row.</t>
+          <t>Borders must not change the page layout unexpectedly.</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q16-sticky-section-header.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q16-add-border-variations.html</t>
         </is>
       </c>
     </row>
@@ -1416,42 +1416,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7. Fixed Support Button</t>
+          <t>17. Apply Rounded Corners</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Place a support button fixed at the bottom-right of the viewport.</t>
+          <t>Use border-radius to style cards, buttons, avatars, and tags.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>A production web app needs a persistent support action.</t>
+          <t>A profile page needs a softer visual style.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Use position: fixed and z-index.</t>
+          <t>Use different radius values based on component shape.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Button must remain visible above page content.</t>
+          <t>Avatar must appear circular.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q17-fixed-support-button.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q17-apply-rounded-corners.html</t>
         </is>
       </c>
     </row>
@@ -1468,42 +1468,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>8. Layered Modal Overlay</t>
+          <t>18. Practice Opacity</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Use z-index and positioning to create a modal over a dimmed background.</t>
+          <t>Create disabled, muted, and overlay styles using opacity.</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>A CRUD interface needs a confirmation dialog.</t>
+          <t>A UI needs inactive controls and secondary text.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Create separate overlay and modal layers.</t>
+          <t>Use opacity only where it does not harm readability.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Modal must appear above overlay.</t>
+          <t>Main text must remain fully readable.</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q18-layered-modal-overlay.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q18-practice-opacity.html</t>
         </is>
       </c>
     </row>
@@ -1520,42 +1520,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>9. Grid Gallery Layout</t>
+          <t>19. Group Shared Selectors</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Create a responsive image gallery using CSS Grid auto-fit/minmax.</t>
+          <t>Use grouped selectors to apply shared styles to headings, buttons, and cards.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>A portfolio project gallery needs automatic columns.</t>
+          <t>A beginner CSS file has repeated declarations.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Use repeat(auto-fit, minmax()).</t>
+          <t>Group selectors that share the same declarations.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Gallery items must keep equal gaps.</t>
+          <t>Do not group selectors with different behavior.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q19-grid-gallery-layout.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q19-group-shared-selectors.html</t>
         </is>
       </c>
     </row>
@@ -1572,42 +1572,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CSS Layout Systems</t>
+          <t>CSS3 Fundamentals</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>10. Flex Form Controls</t>
+          <t>20. Create Simple Utility Classes</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Use Flexbox to align form input and submit button in a single row.</t>
+          <t>Write utility classes for margin, padding, text color, and background color.</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>A newsletter form should look compact on desktop.</t>
+          <t>A small project needs reusable CSS helper classes.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Use flex-basis or flex-grow for the input.</t>
+          <t>Keep each utility class focused on one property.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Input should take remaining width.</t>
+          <t>Do not combine unrelated styles in one utility.</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+          <t>&lt;div class="card"&gt;&lt;h2&gt;Course Title&lt;/h2&gt;&lt;p&gt;Short description&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q20-flex-form-controls.html</t>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q20-create-simple-utility-classes.html</t>
         </is>
       </c>
     </row>
@@ -1624,2095 +1624,5235 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>1. Flex Navbar Alignment</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Use Flexbox to align logo, links, and action button in one responsive navbar row.</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>A dashboard header needs predictable horizontal alignment.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Use justify-content and align-items on the navbar container.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Do not use floats. Keep the logo on the left and button on the right.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q21-flex-navbar-alignment.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="92" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>2. Responsive Card Row</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Arrange four feature cards with Flexbox and wrapping.</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>A course overview page must show cards neatly across screen sizes.</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Use flex-wrap and gap.</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Cards must not overlap when the viewport is narrow.</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q22-responsive-card-row.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="92" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>3. Two Column Portfolio Layout</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Use CSS Grid to create a profile section with content and image columns.</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>A personal portfolio needs a clean intro block.</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Use grid-template-columns and align-items.</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>At desktop width, text must appear before image.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q23-two-column-portfolio-layout.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="92" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>4. Analytics Dashboard Grid</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Build a dashboard layout with CSS Grid areas for sidebar, header, metrics, and chart.</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>An API-driven analytics dashboard needs a repeatable page structure.</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Name grid areas clearly.</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Sidebar must keep a fixed width on desktop.</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q24-analytics-dashboard-grid.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="92" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>5. Absolute Badge Position</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Position a notification badge on the top-right corner of a card.</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>A UI card needs a small unread-count badge.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Set the card to relative and the badge to absolute.</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Badge must stay inside the card boundary.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q25-absolute-badge-position.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="92" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>6. Sticky Section Header</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Create a sticky table toolbar that stays visible while scrolling.</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>An LMS table of learners has many rows.</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Use position: sticky with a top offset.</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Toolbar must not cover the first row.</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q26-sticky-section-header.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="92" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>7. Fixed Support Button</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Place a support button fixed at the bottom-right of the viewport.</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>A production web app needs a persistent support action.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Use position: fixed and z-index.</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Button must remain visible above page content.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q27-fixed-support-button.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="92" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>8. Layered Modal Overlay</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Use z-index and positioning to create a modal over a dimmed background.</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>A CRUD interface needs a confirmation dialog.</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Create separate overlay and modal layers.</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Modal must appear above overlay.</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q28-layered-modal-overlay.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="92" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>9. Grid Gallery Layout</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Create a responsive image gallery using CSS Grid auto-fit/minmax.</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>A portfolio project gallery needs automatic columns.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Use repeat(auto-fit, minmax()).</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Gallery items must keep equal gaps.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q29-grid-gallery-layout.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="92" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>10. Flex Form Controls</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Use Flexbox to align form input and submit button in a single row.</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>A newsletter form should look compact on desktop.</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Use flex-basis or flex-grow for the input.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Input should take remaining width.</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q30-flex-form-controls.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="92" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>11. Center Content With Flexbox</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Use Flexbox to center a card horizontally and vertically inside a section.</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>A login screen needs a centered form card.</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Apply display flex to the parent container.</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Do not use absolute positioning.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q31-center-content-with-flexbox.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="92" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>12. Build Equal Width Columns</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Create three equal-width columns using Flexbox.</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>A feature section displays three benefits side by side.</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Use flex: 1 on child items.</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Columns must keep equal width on desktop.</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q32-build-equal-width-columns.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="92" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>13. Create a Simple Grid</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Use CSS Grid to arrange six boxes into two columns.</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>A beginner dashboard shows quick action tiles.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Use grid-template-columns and gap.</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>No floats or table layout allowed.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q33-create-a-simple-grid.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="92" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>14. Make a Header Layout</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Place logo, search box, and profile action in a single header row.</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>An LMS dashboard needs a compact top bar.</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Use Flexbox alignment and gap.</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Search box should take available space.</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q34-make-a-header-layout.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="92" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>15. Position a Close Icon</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Use absolute positioning to place a close icon in the top-right of a notice.</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>An announcement banner needs a dismiss icon.</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Set the notice container to position relative.</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>The icon must remain inside the notice box.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q35-position-a-close-icon.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="92" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>16. Create a Sticky Navbar</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Make a navigation bar stick to the top during scroll.</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>A long course page needs persistent navigation.</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Use position sticky and top.</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Navbar must remain above page content.</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q36-create-a-sticky-navbar.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="92" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>17. Stack Cards With Gap</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Use flex-direction column and gap to stack cards consistently.</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>A mobile page lists assignments vertically.</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Use gap instead of margin hacks.</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Spacing between all cards must be equal.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q37-stack-cards-with-gap.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="92" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>18. Create Grid Sidebar Layout</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Build a page layout with sidebar and main content using grid columns.</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>A practice platform has left navigation and main questions.</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Use grid-template-columns.</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Sidebar must stay narrower than main content.</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q38-create-grid-sidebar-layout.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="92" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>19. Control Z Index Layers</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Layer a dropdown menu above cards using z-index.</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>A header dropdown is hidden behind content.</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Use positioned elements before z-index.</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown must appear above the page cards.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q39-control-z-index-layers.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="92" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>CSS Layout Systems</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>20. Align Items in a Toolbar</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Align toolbar buttons to the right while keeping the title on the left.</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>A table toolbar needs actions grouped on the right.</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Use justify-content space-between.</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Toolbar items must remain vertically centered.</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>&lt;section class="layout-challenge"&gt;&lt;div&gt;Item 1&lt;/div&gt;&lt;div&gt;Item 2&lt;/div&gt;&lt;div&gt;Item 3&lt;/div&gt;&lt;/section&gt;</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q40-align-items-in-a-toolbar.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="92" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>1. Mobile First Navbar</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Create a vertical mobile navbar that becomes horizontal at 768px.</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>A responsive portfolio must work on phone and desktop.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>Write base mobile styles first, then add a media query.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>Use @media (min-width: 768px).</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q21-mobile-first-navbar.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="92" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q41-mobile-first-navbar.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="92" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>2. Responsive Card Grid</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>Make a one-column card list become two and then three columns on larger screens.</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>A course catalog needs adaptive card columns.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Use CSS Grid and media queries.</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Must start as one column on small screens.</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q22-responsive-card-grid.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="92" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q42-responsive-card-grid.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="92" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>3. Fluid Hero Sizing</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Use %, rem, vh, and max-width to build a hero section that scales cleanly.</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>A landing page hero should fill most of the first screen.</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Use min-height and max-width constraints.</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>Do not use fixed pixel widths for the main container.</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q23-fluid-hero-sizing.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="92" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q43-fluid-hero-sizing.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="92" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>4. Responsive Form Layout</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Stack form fields on mobile and place related fields side by side on desktop.</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>A student registration form needs comfortable mobile entry.</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>Use grid or flex with a breakpoint.</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>Labels must stay above their fields.</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q24-responsive-form-layout.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="92" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q44-responsive-form-layout.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="92" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>5. Adaptive Dashboard Panels</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Switch dashboard widgets from one column to multiple columns using media queries.</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>An analytics dashboard should be usable on tablets and laptops.</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>Define breakpoints for tablet and desktop.</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>Widgets must preserve readable spacing.</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q25-adaptive-dashboard-panels.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="92" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q45-adaptive-dashboard-panels.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="92" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>6. Responsive Image Treatment</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Make images scale without distortion and keep cards stable.</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>A portfolio project card uses screenshots of different sizes.</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Use max-width, height:auto, and object-fit where needed.</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>Images must not overflow their containers.</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q26-responsive-image-treatment.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="92" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q46-responsive-image-treatment.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="92" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>7. Viewport Based Split Section</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Build a section with full viewport height on desktop and natural height on mobile.</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>A product page has a visual section that feels cramped on phones.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>Use vh carefully and override it in a media query.</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>Mobile content must not be clipped.</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q27-viewport-based-split-section.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="92" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q47-viewport-based-split-section.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="92" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>8. Responsive Table Alternative</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Transform a wide data table into stacked blocks on small screens.</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>An LMS progress table is too wide for phone screens.</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Use CSS display changes inside a max-width media query.</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>Each mobile row must show label and value.</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q28-responsive-table-alternative.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="92" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q48-responsive-table-alternative.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="92" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>9. Scalable Spacing System</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Use rem and CSS custom properties for spacing that adapts consistently.</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>A frontend project needs maintainable responsive spacing.</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>Define spacing variables on :root.</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>Avoid hardcoding repeated pixel spacing.</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q29-scalable-spacing-system.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="92" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q49-scalable-spacing-system.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="92" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Responsive Web Design</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>10. Accessible Responsive Footer</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>Create a footer that stacks links on mobile and aligns columns on desktop.</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>A production site footer should remain readable on all devices.</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Use flex or grid with a breakpoint.</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Link tap targets must be at least 44px high on mobile.</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>Viewport: 375px and 1024px
 HTML: Provided responsive component markup</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q30-accessible-responsive-footer.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="92" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q50-accessible-responsive-footer.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="92" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>11. Write Your First Media Query</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Change a card width and padding when the screen is below 600px.</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>A desktop card feels too wide on phones.</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Use @media (max-width: 600px).</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Mobile card must fit within the viewport.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q51-write-your-first-media-query.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="92" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>12. Use Mobile First CSS</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Write base mobile styles and add desktop styles at 768px.</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>A beginner portfolio should be designed for phones first.</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Put mobile styles outside the media query.</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Desktop rules must use min-width.</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q52-use-mobile-first-css.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="92" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>13. Make Text Responsive</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Use rem units and max-width to keep text readable across screen sizes.</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>A lesson page text is too small on desktop and too wide on large screens.</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Set body font size and paragraph max-width.</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Do not use viewport-width font sizing.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q53-make-text-responsive.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="92" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>14. Responsive Button Group</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Stack buttons on mobile and display them inline on desktop.</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>A form has primary and secondary actions.</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Use flex-direction and a breakpoint.</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Buttons must remain easy to tap on mobile.</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q54-responsive-button-group.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="92" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>15. Hide Decorative Content on Mobile</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Hide a decorative image on small screens and show it on desktop.</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>A portfolio hero has an image that crowds the mobile layout.</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Use display none in a media query.</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Do not hide important content.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q55-hide-decorative-content-on-mobile.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="92" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>16. Responsive Pricing Cards</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Show pricing cards in one column on mobile and three columns on desktop.</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>A landing page has three pricing plans.</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Use grid and a min-width breakpoint.</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Cards must not overflow on mobile.</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q56-responsive-pricing-cards.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="92" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>17. Fluid Image Banner</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Make a banner image scale to the container while preserving aspect ratio.</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>A course page has a wide banner image.</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Use width 100% and height auto.</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Image must not appear stretched.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q57-fluid-image-banner.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="92" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>18. Responsive Spacing Tokens</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Increase section padding on desktop while keeping compact mobile padding.</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>A page needs more breathing room on larger screens.</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Use CSS variables or media queries.</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Mobile spacing must remain compact.</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q58-responsive-spacing-tokens.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="92" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>19. Responsive Sidebar Collapse</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Stack sidebar above content on mobile and place it left on desktop.</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>A dashboard must work on phones.</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Use grid or flex with a breakpoint.</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Content must appear below navigation on mobile.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q59-responsive-sidebar-collapse.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="92" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Responsive Web Design</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>20. Prevent Horizontal Scroll</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Fix layout styles that cause unwanted horizontal scrolling.</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>A learner opens a page on mobile and sees sideways scroll.</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Check fixed widths and use max-width.</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Page width must not exceed viewport width.</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>Viewport: 375px and 1024px
+HTML: Provided responsive component markup</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q60-prevent-horizontal-scroll.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="92" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>1. Tailwind Profile Card</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>Use Tailwind utility classes to build a centered profile card.</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>A React portfolio component needs fast utility-first styling.</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>Use spacing, text, border, and shadow utilities.</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>Do not write custom CSS.</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-profile-card"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q31-tailwind-profile-card.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="92" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q61-tailwind-profile-card.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="92" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>2. Tailwind Responsive Navbar</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>Use Tailwind responsive prefixes to stack nav links on mobile and align them on desktop.</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>A production React frontend needs a responsive header.</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Use md:flex and gap utilities.</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>Mobile layout must remain readable.</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-responsive-navbar"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q32-tailwind-responsive-navbar.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="92" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q62-tailwind-responsive-navbar.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="92" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>3. Tailwind Course Grid</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Create a responsive grid of course cards with Tailwind grid utilities.</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>An LMS catalog page shows multiple course cards.</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>Use grid-cols-1, md:grid-cols-2, and lg:grid-cols-3.</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>Cards must have equal spacing.</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-course-grid"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q33-tailwind-course-grid.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="92" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q63-tailwind-course-grid.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="92" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>4. Tailwind Button States</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>Style primary, secondary, and danger buttons with hover and focus utilities.</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>A CRUD UI requires clear action buttons.</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Use hover:, focus:, and ring utilities.</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>Buttons must include visible focus styling.</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-button-states"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q34-tailwind-button-states.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="92" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q64-tailwind-button-states.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="92" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>5. Tailwind Form Panel</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Build a form panel using Tailwind spacing, border, rounded, and input utilities.</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>A dashboard needs a filter form.</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>Apply classes directly to labels and inputs.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>Inputs must be full width.</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-form-panel"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q35-tailwind-form-panel.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="92" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q65-tailwind-form-panel.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="92" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>6. Tailwind Sidebar Layout</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>Create a sidebar plus content layout using Tailwind flex and width utilities.</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>An analytics dashboard needs persistent navigation.</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>Use min-h-screen, w-64, and flex utilities.</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>Sidebar should remain left aligned on desktop.</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-sidebar-layout"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q36-tailwind-sidebar-layout.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="92" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q66-tailwind-sidebar-layout.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="92" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>7. Tailwind Theme Color Usage</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>Use a custom brand color token in Tailwind classes.</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>A frontend team wants brand-consistent components.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>Assume the theme has brand colors configured.</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>Use brand utility names consistently.</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-theme-color-usage"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q37-tailwind-theme-color-usage.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="92" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q67-tailwind-theme-color-usage.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="92" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>8. Tailwind Spacing System</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>Convert raw CSS spacing into Tailwind padding and margin utilities.</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>A team is migrating a component from CSS to Tailwind.</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>Map spacing values to closest Tailwind scale.</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>Do not use arbitrary values unless necessary.</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-spacing-system"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q38-tailwind-spacing-system.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="92" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q68-tailwind-spacing-system.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="92" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>9. Tailwind Dashboard Widgets</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>Style metric widgets with grid, typography, and background utilities.</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>An API dashboard displays KPI cards.</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>Use grid utilities and semantic text sizes.</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>Widgets must align in a responsive grid.</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-dashboard-widgets"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q39-tailwind-dashboard-widgets.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="92" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q69-tailwind-dashboard-widgets.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="92" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>10. Tailwind Production Component</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>Build a reusable alert component using Tailwind utility classes.</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>A production app needs success, info, and error alerts.</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>Use shared base classes and variant classes.</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>Each variant must have accessible contrast.</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>&lt;div class="challenge tailwind-production-component"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q40-tailwind-production-component.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="92" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q70-tailwind-production-component.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="92" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>11. Tailwind Text Styling</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Apply Tailwind classes for font size, weight, color, and line height.</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>A lesson card needs clean text hierarchy.</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Use text, font, leading, and color utilities.</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Do not write custom CSS.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-text-styling"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q71-tailwind-text-styling.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="92" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>12. Tailwind Spacing Practice</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Use Tailwind margin and padding utilities to space a card.</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>A beginner component has cramped content.</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Use p, m, mt, and gap utilities.</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Avoid arbitrary values.</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-spacing-practice"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q72-tailwind-spacing-practice.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="92" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>13. Tailwind Flex Centering</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Center a login card using Tailwind flex utilities.</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>A sign-in page needs centered content.</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Use min-h-screen, flex, items-center, and justify-center.</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Do not use custom CSS.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-flex-centering"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q73-tailwind-flex-centering.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="92" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>14. Tailwind Color Badges</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Create three status badges using Tailwind background and text color classes.</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>A task list shows pending, complete, and failed states.</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>Use rounded-full and px/py utilities.</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Badge colors must be readable.</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-color-badges"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q74-tailwind-color-badges.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="92" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>15. Tailwind Border Card</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Build a card with border, rounded corners, padding, and shadow.</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>A course catalog displays course tiles.</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Use border, rounded, p, and shadow utilities.</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Card must have visible spacing.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-border-card"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q75-tailwind-border-card.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="92" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>16. Tailwind Responsive Text</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Change heading size at the md breakpoint.</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>A hero heading should be smaller on phones and larger on desktop.</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Use text-2xl and md:text-4xl style classes.</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Base class must support mobile first.</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-responsive-text"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q76-tailwind-responsive-text.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="92" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>17. Tailwind Grid Basics</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Create a one-column mobile grid that becomes two columns at md.</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>A project list needs responsive columns.</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Use grid, grid-cols-1, md:grid-cols-2, and gap.</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>No custom media query allowed.</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-grid-basics"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q77-tailwind-grid-basics.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="92" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>18. Tailwind Form Inputs</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Style input fields with border, padding, rounded corners, and focus ring.</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>A filter form needs consistent input styling.</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Use focus:ring and focus:border utilities.</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Focus state must be visible.</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-form-inputs"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q78-tailwind-form-inputs.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="92" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>19. Tailwind Button Hover</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Add hover background change to a primary button.</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>A call-to-action button needs interaction feedback.</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Use hover: utilities.</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Button text must remain readable on hover.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-button-hover"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q79-tailwind-button-hover.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="92" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Tailwind CSS</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>20. Tailwind Simple Alert</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Create an alert box using Tailwind background, border, text, and spacing classes.</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>A form page shows validation feedback.</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>Use utility classes only.</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Alert must include comfortable padding.</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>&lt;div class="challenge tailwind-simple-alert"&gt;Apply Tailwind classes to match the requested UI.&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q80-tailwind-simple-alert.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="92" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>1. Hoverable Dashboard Card</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Add hover transitions and transform effects to dashboard cards.</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>An analytics dashboard should feel interactive without JavaScript.</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>Use transition and transform properties.</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>Hover effect must be subtle and not shift layout.</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q41-hoverable-dashboard-card.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="92" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q81-hoverable-dashboard-card.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="92" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>2. Animated Submit Button</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>Create a button with hover, active, and disabled states.</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>A form submission UI needs clear interaction feedback.</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>Use pseudo-classes and transitions.</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>Disabled state must look inactive and block pointer styling.</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q42-animated-submit-button.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="92" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q82-animated-submit-button.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="92" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>3. Skeleton Loading Card</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>Build a CSS-only loading skeleton for a card layout.</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>API data may take time to load in a dashboard.</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>Use gradients and keyframe animation.</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>Animation should be smooth and not distract users.</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q43-skeleton-loading-card.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="92" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q83-skeleton-loading-card.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="92" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>4. Sidebar Navigation States</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>Style active, hover, and focus states for sidebar links.</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>A dashboard sidebar must show where the user is.</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>Use classes for active state and pseudo-classes for interactions.</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>Active state must differ from hover state.</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q44-sidebar-navigation-states.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="92" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q84-sidebar-navigation-states.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="92" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>5. Interactive Form Feedback</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>Style valid, invalid, and focus states for form inputs.</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>A CRUD form should guide users as they type.</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>Use :focus, :valid, and :invalid selectors.</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>Invalid state must not rely only on color.</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q45-interactive-form-feedback.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="92" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q85-interactive-form-feedback.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="92" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>6. Card Widget Hierarchy</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Design a KPI widget with strong visual hierarchy using typography, color, and spacing.</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>A dashboard shows revenue, users, and conversion metrics.</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>Use heading, value, and helper text styles.</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>The metric value must be the most prominent element.</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q46-card-widget-hierarchy.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="92" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q86-card-widget-hierarchy.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="92" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>7. Fade In Content Section</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>Add a fade-in animation to newly visible content.</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>A React page renders panels after data loads.</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G88" s="4" t="inlineStr">
         <is>
           <t>Use @keyframes and animation properties.</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>Animation duration must be under 500ms.</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q47-fade-in-content-section.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="92" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q87-fade-in-content-section.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="92" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>8. Accessible Tooltip Styling</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Create a CSS tooltip that appears on hover and focus.</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>Icon buttons need short helper text.</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>Use position and opacity transitions.</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>Tooltip must work with keyboard focus.</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q48-accessible-tooltip-styling.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="92" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q88-accessible-tooltip-styling.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="92" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>9. Interactive Modal Motion</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>Style a modal with overlay fade and panel scale animation.</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>A production UI opens confirmation dialogs.</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>Use transform, opacity, and transition.</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>Respect reduced motion with a media query.</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I90" s="4" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q49-interactive-modal-motion.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="92" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q89-interactive-modal-motion.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="92" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UI Design Concepts</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>10. Empty State Panel</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>Design an empty state with icon area, message, and action button.</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>A dashboard has no records after filters are applied.</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>Use layout, spacing, and subtle color hierarchy.</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>The action button must remain visually prominent.</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
 &lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q50-empty-state-panel.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="92" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q90-empty-state-panel.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="92" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>11. Button Hover Feedback</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Create a button hover effect using color and transition.</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>A practice page button should respond when hovered.</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Use transition on the button.</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Hover must not change button size.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q91-button-hover-feedback.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="92" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>12. Card Hover Shadow</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Add a subtle shadow on card hover.</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>A course list should show which card is interactive.</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>Use box-shadow and transition.</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>The card must not jump on hover.</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q92-card-hover-shadow.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="92" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>13. Input Focus State</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Style an input field when focused.</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>A form should clearly show the active field.</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Use :focus and outline or box-shadow.</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Do not remove focus feedback.</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q93-input-focus-state.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="92" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>14. Simple Loading State</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Style a disabled loading button.</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>A submit button shows that work is in progress.</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Use opacity and cursor styles.</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>Button must look disabled.</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q94-simple-loading-state.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="92" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>15. Create Active Menu Item</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Style the currently selected sidebar item.</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>A dashboard menu should identify the active page.</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Use an active class.</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Active state must be visually stronger than hover.</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q95-create-active-menu-item.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="92" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>16. Smooth Fade Effect</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Add a simple fade-in animation to a message box.</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>A success message appears after saving.</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>Use @keyframes and animation.</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>Animation must finish quickly.</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q96-smooth-fade-effect.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="92" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>17. Icon Button Tooltip</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Show a small tooltip on hover.</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>A toolbar icon needs a label.</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Use position absolute and opacity.</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Tooltip text must be readable.</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q97-icon-button-tooltip.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="92" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>18. Design Empty State</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Style an empty list message with title, text, and action button.</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>A filtered assignment list has no results.</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Use spacing and visual hierarchy.</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>Primary action must be easy to find.</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q98-design-empty-state.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="92" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>19. Style Error Message</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Create a clear error message below a form field.</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>A form validation error must be obvious.</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Use color, spacing, and helper text.</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Do not rely on color alone.</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q99-style-error-message.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="92" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UI Design Concepts</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>20. Create Transitioned Panel</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Add a transition to a panel that changes background on hover.</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>A settings panel should feel interactive.</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>Use transition-property and duration.</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>Effect must remain subtle.</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>&lt;button class="ui-action"&gt;Save changes&lt;/button&gt;
+&lt;div class="panel"&gt;Dashboard content&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q100-create-transitioned-panel.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="92" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>1. Reusable Component Classes</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>Create scalable CSS classes for buttons with base and variant styles.</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>A React app needs consistent buttons across pages.</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>Separate base class from variant classes.</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>Do not duplicate shared button declarations.</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q51-reusable-component-classes.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="92" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q101-reusable-component-classes.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="92" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>2. Organized CSS Structure</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>Refactor scattered CSS into sections for reset, tokens, layout, components, and utilities.</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <t>A production-ready app has grown beyond one-off styles.</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>Use comments only for major sections.</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>Keep selectors readable and avoid deep nesting.</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q52-organized-css-structure.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="92" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q102-organized-css-structure.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="92" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>3. CSS Variables Theme</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>Create light and dark theme tokens with CSS custom properties.</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>A web app supports theme switching.</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t>Define tokens on :root and override them with a theme class.</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>Components must use variables instead of hardcoded colors.</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="I104" s="4" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q53-css-variables-theme.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="92" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q103-css-variables-theme.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="92" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>4. Accessible Contrast Fix</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>Adjust colors for readable buttons, alerts, and text.</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <t>A QA report says some UI text is hard to read.</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G105" s="6" t="inlineStr">
         <is>
           <t>Choose foreground/background pairs with clear contrast.</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="H105" s="6" t="inlineStr">
         <is>
           <t>Do not reduce font size to solve layout issues.</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I105" s="6" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q54-accessible-contrast-fix.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="92" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q104-accessible-contrast-fix.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="92" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>5. Production Form Component</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E106" s="4" t="inlineStr">
         <is>
           <t>Style a reusable React form component with error, helper, and disabled states.</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>A production CRUD workflow shares form components.</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>Create predictable classes for each state.</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>Error text must be visible and associated with the field visually.</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="I106" s="4" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q55-production-form-component.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="92" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q105-production-form-component.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="92" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>6. Optimize CSS Asset Usage</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
         <is>
           <t>Reduce redundant background images and unnecessary heavy visual effects.</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <t>A production page loads slowly due to styling choices.</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G107" s="6" t="inlineStr">
         <is>
           <t>Prefer CSS gradients or optimized reusable assets.</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>Do not remove required brand visuals.</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I107" s="6" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q56-optimize-css-asset-usage.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="92" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q106-optimize-css-asset-usage.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="92" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>7. Component Scoped Naming</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
         <is>
           <t>Create class names using a clear component naming convention.</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>A large frontend team needs styles that do not collide.</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G108" s="4" t="inlineStr">
         <is>
           <t>Use a consistent prefix or BEM-style naming.</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="H108" s="4" t="inlineStr">
         <is>
           <t>Class names must communicate component ownership.</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="I108" s="4" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q57-component-scoped-naming.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="92" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q107-component-scoped-naming.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="92" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>8. Production Dashboard Layout</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>Style a full dashboard shell with header, sidebar, content, and responsive behavior.</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <t>A React analytics frontend is ready for deployment.</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G109" s="6" t="inlineStr">
         <is>
           <t>Use reusable layout classes and responsive rules.</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>The shell must remain usable on mobile.</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q58-production-dashboard-layout.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="92" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q108-production-dashboard-layout.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="92" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>9. Semantic UI Styling</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>Style semantic HTML elements without breaking accessibility.</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>A production page uses header, main, section, nav, and footer tags.</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G110" s="4" t="inlineStr">
         <is>
           <t>Use semantic selectors carefully with classes for components.</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H110" s="4" t="inlineStr">
         <is>
           <t>Do not remove outlines or hide labels.</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="I110" s="4" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q59-semantic-ui-styling.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="92" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Beginner</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q109-semantic-ui-styling.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="92" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>Production-Level Frontend Styling</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>10. Performance Friendly Animation</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>Rewrite animations to use transform and opacity instead of layout-changing properties.</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>A UI animation causes jank on lower-end devices.</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>Animate transform and opacity only where possible.</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H111" s="6" t="inlineStr">
         <is>
           <t>Avoid animating width, height, top, or left.</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
+      <c r="I111" s="6" t="inlineStr">
         <is>
           <t>Existing component classes and semantic HTML from a React frontend</t>
         </is>
       </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q60-performance-friendly-animation.html</t>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q110-performance-friendly-animation.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="92" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>11. Create Design Tokens</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Define CSS variables for colors, spacing, and radius.</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>A growing frontend project needs consistent values.</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>Use :root custom properties.</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>Components must reference the variables.</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q111-create-design-tokens.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="92" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>12. Reusable Button System</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>Create base, primary, and secondary button classes.</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>A React app repeats button styles in many places.</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>Use a shared base class and variants.</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>Avoid duplicate declarations.</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q112-reusable-button-system.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="92" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>13. Reusable Card Component</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Write card classes for container, title, body, and footer.</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>A dashboard uses cards across pages.</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>Use component-based class names.</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>Class names must be predictable.</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q113-reusable-card-component.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="92" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>14. Accessible Focus Styles</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>Add consistent focus-visible styles for links, buttons, and inputs.</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>Keyboard users must see where they are on the page.</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>Use :focus-visible.</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>Do not set outline to none without replacement.</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q114-accessible-focus-styles.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="92" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>15. Organize CSS File Sections</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Arrange CSS into reset, variables, base, layout, components, and utilities.</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>A project CSS file is becoming difficult to maintain.</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>Use short section comments.</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>Do not change behavior while organizing.</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q115-organize-css-file-sections.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="92" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>16. Use Semantic Layout Classes</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>Style header, main, nav, section, and footer regions with classes.</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>A production page uses semantic HTML.</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>Use classes for component-specific styling.</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>Do not depend only on tag selectors.</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q116-use-semantic-layout-classes.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="92" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>17. Reduce Repeated Colors</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Replace repeated color values with CSS variables.</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>A code review finds many duplicate color declarations.</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>Create variables and reuse them.</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Keep the visual result unchanged.</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q117-reduce-repeated-colors.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="92" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>18. Safe Animation Choices</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>Use transform and opacity for a small entrance animation.</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>A page animation should be smooth.</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>Avoid animating layout properties.</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>Do not animate width or height.</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q118-safe-animation-choices.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="92" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>19. Responsive Production Shell</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Create layout classes for app shell, sidebar, and main area.</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>A deployed dashboard must work on desktop and mobile.</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>Use a breakpoint to change layout.</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>Mobile layout must remain usable.</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q119-responsive-production-shell.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="92" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Production-Level Frontend Styling</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>20. Accessible Color States</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>Style success, warning, and error states with readable text and non-color cues.</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>Production alerts must be understandable to all users.</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>Use icons, borders, or labels in addition to color.</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>Contrast must be readable.</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>Existing component classes and semantic HTML from a React frontend</t>
+        </is>
+      </c>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t>https://htmlpreview.github.io/?https://github.com/Nithya-sri-14/css-beginner/blob/main/question-bank/outputs/q120-accessible-color-states.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J61"/>
+  <autoFilter ref="A1:J121"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -3774,10 +6914,70 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId61"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId121"/>
   </tableParts>
 </worksheet>
 </file>
--- a/question-bank/CSS_Question_Bank.xlsx
+++ b/question-bank/CSS_Question_Bank.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>A student portal needs profile cards for enrolled learners.</t>
+          <t>A student portal needs profile cards for enrolled learners. The learner is given a small HTML snippet for 'Style a Profile Card' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>A blog article page is hard to read on desktop screens.</t>
+          <t>A blog article page is hard to read on desktop screens. The learner is given a small HTML snippet for 'Format Article Typography' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>A dashboard needs clear status labels for tasks.</t>
+          <t>A dashboard needs clear status labels for tasks. The learner is given a small HTML snippet for 'Create a Color Badge Set' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>A pricing page has cards that look uneven because spacing is inconsistent.</t>
+          <t>A pricing page has cards that look uneven because spacing is inconsistent. The learner is given a small HTML snippet for 'Apply the Box Model' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>An LMS login form needs a clean CSS-only visual update.</t>
+          <t>An LMS login form needs a clean CSS-only visual update. The learner is given a small HTML snippet for 'Style a Login Form' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>A course landing banner should have a modern CSS3 background.</t>
+          <t>A course landing banner should have a modern CSS3 background. The learner is given a small HTML snippet for 'Add Background Effects' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>A portfolio website needs a clean header with links.</t>
+          <t>A portfolio website needs a clean header with links. The learner is given a small HTML snippet for 'Build a Navigation Bar' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>An ecommerce practice page highlights one selected product.</t>
+          <t>An ecommerce practice page highlights one selected product. The learner is given a small HTML snippet for 'Design a Product Tile' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>A new HTML page has inconsistent browser default margins.</t>
+          <t>A new HTML page has inconsistent browser default margins. The learner is given a small HTML snippet for 'Normalize Page Spacing' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>A small design system needs simple typography helpers.</t>
+          <t>A small design system needs simple typography helpers. The learner is given a small HTML snippet for 'Create Text Utility Classes' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>An LMS lesson page needs clear heading hierarchy.</t>
+          <t>An LMS lesson page needs clear heading hierarchy. The learner is given a small HTML snippet for 'Style Heading Levels' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>A documentation page needs readable and accessible links.</t>
+          <t>A documentation page needs readable and accessible links. The learner is given a small HTML snippet for 'Create Link Styles' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>A practice platform shows feedback after code submission.</t>
+          <t>A practice platform shows feedback after code submission. The learner is given a small HTML snippet for 'Build Alert Boxes' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>A coding lesson page needs different text styles for prose and code.</t>
+          <t>A coding lesson page needs different text styles for prose and code. The learner is given a small HTML snippet for 'Use Font Families Correctly' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>A course article should not stretch too wide on large screens.</t>
+          <t>A course article should not stretch too wide on large screens. The learner is given a small HTML snippet for 'Control Element Widths' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>A notes page needs different callout styles.</t>
+          <t>A notes page needs different callout styles. The learner is given a small HTML snippet for 'Add Border Variations' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>A profile page needs a softer visual style.</t>
+          <t>A profile page needs a softer visual style. The learner is given a small HTML snippet for 'Apply Rounded Corners' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>A UI needs inactive controls and secondary text.</t>
+          <t>A UI needs inactive controls and secondary text. The learner is given a small HTML snippet for 'Practice Opacity' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>A beginner CSS file has repeated declarations.</t>
+          <t>A beginner CSS file has repeated declarations. The learner is given a small HTML snippet for 'Group Shared Selectors' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>A small project needs reusable CSS helper classes.</t>
+          <t>A small project needs reusable CSS helper classes. The learner is given a small HTML snippet for 'Create Simple Utility Classes' and must style it to match the expected output shown in the sample link. This task appears in the foundation section of the LMS, where learners are expected to prove that they can translate a simple visual requirement into correct CSS selectors and declarations. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>A dashboard header needs predictable horizontal alignment.</t>
+          <t>A dashboard header needs predictable horizontal alignment. The learner is given a small HTML snippet for 'Flex Navbar Alignment' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>A course overview page must show cards neatly across screen sizes.</t>
+          <t>A course overview page must show cards neatly across screen sizes. The learner is given a small HTML snippet for 'Responsive Card Row' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>A personal portfolio needs a clean intro block.</t>
+          <t>A personal portfolio needs a clean intro block. The learner is given a small HTML snippet for 'Two Column Portfolio Layout' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>An API-driven analytics dashboard needs a repeatable page structure.</t>
+          <t>An API-driven analytics dashboard needs a repeatable page structure. The learner is given a small HTML snippet for 'Analytics Dashboard Grid' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>A UI card needs a small unread-count badge.</t>
+          <t>A UI card needs a small unread-count badge. The learner is given a small HTML snippet for 'Absolute Badge Position' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>An LMS table of learners has many rows.</t>
+          <t>An LMS table of learners has many rows. The learner is given a small HTML snippet for 'Sticky Section Header' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>A production web app needs a persistent support action.</t>
+          <t>A production web app needs a persistent support action. The learner is given a small HTML snippet for 'Fixed Support Button' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>A CRUD interface needs a confirmation dialog.</t>
+          <t>A CRUD interface needs a confirmation dialog. The learner is given a small HTML snippet for 'Layered Modal Overlay' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>A portfolio project gallery needs automatic columns.</t>
+          <t>A portfolio project gallery needs automatic columns. The learner is given a small HTML snippet for 'Grid Gallery Layout' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>A newsletter form should look compact on desktop.</t>
+          <t>A newsletter form should look compact on desktop. The learner is given a small HTML snippet for 'Flex Form Controls' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>A login screen needs a centered form card.</t>
+          <t>A login screen needs a centered form card. The learner is given a small HTML snippet for 'Center Content With Flexbox' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>A feature section displays three benefits side by side.</t>
+          <t>A feature section displays three benefits side by side. The learner is given a small HTML snippet for 'Build Equal Width Columns' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>A beginner dashboard shows quick action tiles.</t>
+          <t>A beginner dashboard shows quick action tiles. The learner is given a small HTML snippet for 'Create a Simple Grid' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>An LMS dashboard needs a compact top bar.</t>
+          <t>An LMS dashboard needs a compact top bar. The learner is given a small HTML snippet for 'Make a Header Layout' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>An announcement banner needs a dismiss icon.</t>
+          <t>An announcement banner needs a dismiss icon. The learner is given a small HTML snippet for 'Position a Close Icon' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>A long course page needs persistent navigation.</t>
+          <t>A long course page needs persistent navigation. The learner is given a small HTML snippet for 'Create a Sticky Navbar' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>A mobile page lists assignments vertically.</t>
+          <t>A mobile page lists assignments vertically. The learner is given a small HTML snippet for 'Stack Cards With Gap' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>A practice platform has left navigation and main questions.</t>
+          <t>A practice platform has left navigation and main questions. The learner is given a small HTML snippet for 'Create Grid Sidebar Layout' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>A header dropdown is hidden behind content.</t>
+          <t>A header dropdown is hidden behind content. The learner is given a small HTML snippet for 'Control Z Index Layers' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>A table toolbar needs actions grouped on the right.</t>
+          <t>A table toolbar needs actions grouped on the right. The learner is given a small HTML snippet for 'Align Items in a Toolbar' and must style it to match the expected output shown in the sample link. This task appears in the layout practice section, where learners must arrange real interface blocks using Flexbox, Grid, or positioning instead of relying on trial-and-error spacing. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>A responsive portfolio must work on phone and desktop.</t>
+          <t>A responsive portfolio must work on phone and desktop. The learner is given a small HTML snippet for 'Mobile First Navbar' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>A course catalog needs adaptive card columns.</t>
+          <t>A course catalog needs adaptive card columns. The learner is given a small HTML snippet for 'Responsive Card Grid' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>A landing page hero should fill most of the first screen.</t>
+          <t>A landing page hero should fill most of the first screen. The learner is given a small HTML snippet for 'Fluid Hero Sizing' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>A student registration form needs comfortable mobile entry.</t>
+          <t>A student registration form needs comfortable mobile entry. The learner is given a small HTML snippet for 'Responsive Form Layout' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>An analytics dashboard should be usable on tablets and laptops.</t>
+          <t>An analytics dashboard should be usable on tablets and laptops. The learner is given a small HTML snippet for 'Adaptive Dashboard Panels' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>A portfolio project card uses screenshots of different sizes.</t>
+          <t>A portfolio project card uses screenshots of different sizes. The learner is given a small HTML snippet for 'Responsive Image Treatment' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>A product page has a visual section that feels cramped on phones.</t>
+          <t>A product page has a visual section that feels cramped on phones. The learner is given a small HTML snippet for 'Viewport Based Split Section' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>An LMS progress table is too wide for phone screens.</t>
+          <t>An LMS progress table is too wide for phone screens. The learner is given a small HTML snippet for 'Responsive Table Alternative' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>A frontend project needs maintainable responsive spacing.</t>
+          <t>A frontend project needs maintainable responsive spacing. The learner is given a small HTML snippet for 'Scalable Spacing System' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>A production site footer should remain readable on all devices.</t>
+          <t>A production site footer should remain readable on all devices. The learner is given a small HTML snippet for 'Accessible Responsive Footer' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>A desktop card feels too wide on phones.</t>
+          <t>A desktop card feels too wide on phones. The learner is given a small HTML snippet for 'Write Your First Media Query' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>A beginner portfolio should be designed for phones first.</t>
+          <t>A beginner portfolio should be designed for phones first. The learner is given a small HTML snippet for 'Use Mobile First CSS' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>A lesson page text is too small on desktop and too wide on large screens.</t>
+          <t>A lesson page text is too small on desktop and too wide on large screens. The learner is given a small HTML snippet for 'Make Text Responsive' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>A form has primary and secondary actions.</t>
+          <t>A form has primary and secondary actions. The learner is given a small HTML snippet for 'Responsive Button Group' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>A portfolio hero has an image that crowds the mobile layout.</t>
+          <t>A portfolio hero has an image that crowds the mobile layout. The learner is given a small HTML snippet for 'Hide Decorative Content on Mobile' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>A landing page has three pricing plans.</t>
+          <t>A landing page has three pricing plans. The learner is given a small HTML snippet for 'Responsive Pricing Cards' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>A course page has a wide banner image.</t>
+          <t>A course page has a wide banner image. The learner is given a small HTML snippet for 'Fluid Image Banner' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>A page needs more breathing room on larger screens.</t>
+          <t>A page needs more breathing room on larger screens. The learner is given a small HTML snippet for 'Responsive Spacing Tokens' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>A dashboard must work on phones.</t>
+          <t>A dashboard must work on phones. The learner is given a small HTML snippet for 'Responsive Sidebar Collapse' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>A learner opens a page on mobile and sees sideways scroll.</t>
+          <t>A learner opens a page on mobile and sees sideways scroll. The learner is given a small HTML snippet for 'Prevent Horizontal Scroll' and must style it to match the expected output shown in the sample link. This task appears in the responsive design module, where learners must make the same component work across mobile, tablet, and desktop screen sizes. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>A React portfolio component needs fast utility-first styling.</t>
+          <t>A React portfolio component needs fast utility-first styling. The learner is given a small HTML snippet for 'Tailwind Profile Card' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>A production React frontend needs a responsive header.</t>
+          <t>A production React frontend needs a responsive header. The learner is given a small HTML snippet for 'Tailwind Responsive Navbar' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>An LMS catalog page shows multiple course cards.</t>
+          <t>An LMS catalog page shows multiple course cards. The learner is given a small HTML snippet for 'Tailwind Course Grid' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>A CRUD UI requires clear action buttons.</t>
+          <t>A CRUD UI requires clear action buttons. The learner is given a small HTML snippet for 'Tailwind Button States' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>A dashboard needs a filter form.</t>
+          <t>A dashboard needs a filter form. The learner is given a small HTML snippet for 'Tailwind Form Panel' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>An analytics dashboard needs persistent navigation.</t>
+          <t>An analytics dashboard needs persistent navigation. The learner is given a small HTML snippet for 'Tailwind Sidebar Layout' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>A frontend team wants brand-consistent components.</t>
+          <t>A frontend team wants brand-consistent components. The learner is given a small HTML snippet for 'Tailwind Theme Color Usage' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>A team is migrating a component from CSS to Tailwind.</t>
+          <t>A team is migrating a component from CSS to Tailwind. The learner is given a small HTML snippet for 'Tailwind Spacing System' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>An API dashboard displays KPI cards.</t>
+          <t>An API dashboard displays KPI cards. The learner is given a small HTML snippet for 'Tailwind Dashboard Widgets' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>A production app needs success, info, and error alerts.</t>
+          <t>A production app needs success, info, and error alerts. The learner is given a small HTML snippet for 'Tailwind Production Component' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>A lesson card needs clean text hierarchy.</t>
+          <t>A lesson card needs clean text hierarchy. The learner is given a small HTML snippet for 'Tailwind Text Styling' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>A beginner component has cramped content.</t>
+          <t>A beginner component has cramped content. The learner is given a small HTML snippet for 'Tailwind Spacing Practice' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>A sign-in page needs centered content.</t>
+          <t>A sign-in page needs centered content. The learner is given a small HTML snippet for 'Tailwind Flex Centering' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>A task list shows pending, complete, and failed states.</t>
+          <t>A task list shows pending, complete, and failed states. The learner is given a small HTML snippet for 'Tailwind Color Badges' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>A course catalog displays course tiles.</t>
+          <t>A course catalog displays course tiles. The learner is given a small HTML snippet for 'Tailwind Border Card' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>A hero heading should be smaller on phones and larger on desktop.</t>
+          <t>A hero heading should be smaller on phones and larger on desktop. The learner is given a small HTML snippet for 'Tailwind Responsive Text' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>A project list needs responsive columns.</t>
+          <t>A project list needs responsive columns. The learner is given a small HTML snippet for 'Tailwind Grid Basics' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>A filter form needs consistent input styling.</t>
+          <t>A filter form needs consistent input styling. The learner is given a small HTML snippet for 'Tailwind Form Inputs' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>A call-to-action button needs interaction feedback.</t>
+          <t>A call-to-action button needs interaction feedback. The learner is given a small HTML snippet for 'Tailwind Button Hover' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>A form page shows validation feedback.</t>
+          <t>A form page shows validation feedback. The learner is given a small HTML snippet for 'Tailwind Simple Alert' and must style it to match the expected output shown in the sample link. This task appears in the Tailwind CSS practice module, where learners must style the interface using utility classes in the same way they would inside a React component. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>An analytics dashboard should feel interactive without JavaScript.</t>
+          <t>An analytics dashboard should feel interactive without JavaScript. The learner is given a small HTML snippet for 'Hoverable Dashboard Card' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>A form submission UI needs clear interaction feedback.</t>
+          <t>A form submission UI needs clear interaction feedback. The learner is given a small HTML snippet for 'Animated Submit Button' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>API data may take time to load in a dashboard.</t>
+          <t>API data may take time to load in a dashboard. The learner is given a small HTML snippet for 'Skeleton Loading Card' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>A dashboard sidebar must show where the user is.</t>
+          <t>A dashboard sidebar must show where the user is. The learner is given a small HTML snippet for 'Sidebar Navigation States' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>A CRUD form should guide users as they type.</t>
+          <t>A CRUD form should guide users as they type. The learner is given a small HTML snippet for 'Interactive Form Feedback' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>A dashboard shows revenue, users, and conversion metrics.</t>
+          <t>A dashboard shows revenue, users, and conversion metrics. The learner is given a small HTML snippet for 'Card Widget Hierarchy' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>A React page renders panels after data loads.</t>
+          <t>A React page renders panels after data loads. The learner is given a small HTML snippet for 'Fade In Content Section' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Icon buttons need short helper text.</t>
+          <t>Icon buttons need short helper text. The learner is given a small HTML snippet for 'Accessible Tooltip Styling' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>A production UI opens confirmation dialogs.</t>
+          <t>A production UI opens confirmation dialogs. The learner is given a small HTML snippet for 'Interactive Modal Motion' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>A dashboard has no records after filters are applied.</t>
+          <t>A dashboard has no records after filters are applied. The learner is given a small HTML snippet for 'Empty State Panel' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>A practice page button should respond when hovered.</t>
+          <t>A practice page button should respond when hovered. The learner is given a small HTML snippet for 'Button Hover Feedback' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>A course list should show which card is interactive.</t>
+          <t>A course list should show which card is interactive. The learner is given a small HTML snippet for 'Card Hover Shadow' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>A form should clearly show the active field.</t>
+          <t>A form should clearly show the active field. The learner is given a small HTML snippet for 'Input Focus State' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>A submit button shows that work is in progress.</t>
+          <t>A submit button shows that work is in progress. The learner is given a small HTML snippet for 'Simple Loading State' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>A dashboard menu should identify the active page.</t>
+          <t>A dashboard menu should identify the active page. The learner is given a small HTML snippet for 'Create Active Menu Item' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>A success message appears after saving.</t>
+          <t>A success message appears after saving. The learner is given a small HTML snippet for 'Smooth Fade Effect' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>A toolbar icon needs a label.</t>
+          <t>A toolbar icon needs a label. The learner is given a small HTML snippet for 'Icon Button Tooltip' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>A filtered assignment list has no results.</t>
+          <t>A filtered assignment list has no results. The learner is given a small HTML snippet for 'Design Empty State' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>A form validation error must be obvious.</t>
+          <t>A form validation error must be obvious. The learner is given a small HTML snippet for 'Style Error Message' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>A settings panel should feel interactive.</t>
+          <t>A settings panel should feel interactive. The learner is given a small HTML snippet for 'Create Transitioned Panel' and must style it to match the expected output shown in the sample link. This task appears in the interactive UI module, where learners focus on visual feedback, state styling, motion, and user-friendly interface behavior. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>A React app needs consistent buttons across pages.</t>
+          <t>A React app needs consistent buttons across pages. The learner is given a small HTML snippet for 'Reusable Component Classes' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>A production-ready app has grown beyond one-off styles.</t>
+          <t>A production-ready app has grown beyond one-off styles. The learner is given a small HTML snippet for 'Organized CSS Structure' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>A web app supports theme switching.</t>
+          <t>A web app supports theme switching. The learner is given a small HTML snippet for 'CSS Variables Theme' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>A QA report says some UI text is hard to read.</t>
+          <t>A QA report says some UI text is hard to read. The learner is given a small HTML snippet for 'Accessible Contrast Fix' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>A production CRUD workflow shares form components.</t>
+          <t>A production CRUD workflow shares form components. The learner is given a small HTML snippet for 'Production Form Component' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>A production page loads slowly due to styling choices.</t>
+          <t>A production page loads slowly due to styling choices. The learner is given a small HTML snippet for 'Optimize CSS Asset Usage' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>A large frontend team needs styles that do not collide.</t>
+          <t>A large frontend team needs styles that do not collide. The learner is given a small HTML snippet for 'Component Scoped Naming' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>A React analytics frontend is ready for deployment.</t>
+          <t>A React analytics frontend is ready for deployment. The learner is given a small HTML snippet for 'Production Dashboard Layout' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>A production page uses header, main, section, nav, and footer tags.</t>
+          <t>A production page uses header, main, section, nav, and footer tags. The learner is given a small HTML snippet for 'Semantic UI Styling' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>A UI animation causes jank on lower-end devices.</t>
+          <t>A UI animation causes jank on lower-end devices. The learner is given a small HTML snippet for 'Performance Friendly Animation' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>A growing frontend project needs consistent values.</t>
+          <t>A growing frontend project needs consistent values. The learner is given a small HTML snippet for 'Create Design Tokens' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>A React app repeats button styles in many places.</t>
+          <t>A React app repeats button styles in many places. The learner is given a small HTML snippet for 'Reusable Button System' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>A dashboard uses cards across pages.</t>
+          <t>A dashboard uses cards across pages. The learner is given a small HTML snippet for 'Reusable Card Component' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>Keyboard users must see where they are on the page.</t>
+          <t>Keyboard users must see where they are on the page. The learner is given a small HTML snippet for 'Accessible Focus Styles' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>A project CSS file is becoming difficult to maintain.</t>
+          <t>A project CSS file is becoming difficult to maintain. The learner is given a small HTML snippet for 'Organize CSS File Sections' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>A production page uses semantic HTML.</t>
+          <t>A production page uses semantic HTML. The learner is given a small HTML snippet for 'Use Semantic Layout Classes' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>A code review finds many duplicate color declarations.</t>
+          <t>A code review finds many duplicate color declarations. The learner is given a small HTML snippet for 'Reduce Repeated Colors' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>A page animation should be smooth.</t>
+          <t>A page animation should be smooth. The learner is given a small HTML snippet for 'Safe Animation Choices' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>A deployed dashboard must work on desktop and mobile.</t>
+          <t>A deployed dashboard must work on desktop and mobile. The learner is given a small HTML snippet for 'Responsive Production Shell' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>Production alerts must be understandable to all users.</t>
+          <t>Production alerts must be understandable to all users. The learner is given a small HTML snippet for 'Accessible Color States' and must style it to match the expected output shown in the sample link. This task appears in the production styling module, where learners must write maintainable, reusable, accessible CSS suitable for a real frontend codebase. The scenario should be solved as a frontend coding challenge: inspect the class names, write clean CSS, preserve the given markup, and make the final rendered UI visually match the target output.</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">

--- a/question-bank/CSS_Question_Bank.xlsx
+++ b/question-bank/CSS_Question_Bank.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Target the provided class names and avoid inline styles.</t>
+          <t>Inspect the provided markup for 'Style a Profile Card', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Use only CSS3. Do not change the HTML structure.</t>
+          <t>Do not change the provided HTML structure for 'Style a Profile Card'. The submitted CSS must match the sample output for question 1 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Style headings and paragraphs with separate selectors.</t>
+          <t>Style the form controls for 'Format Article Typography' in their normal and focus states; labels, inputs, helper text, and buttons should remain aligned and readable.</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Use rem units for font sizes. Keep body text left aligned.</t>
+          <t>Do not change the provided HTML structure for 'Format Article Typography'. Inputs must remain keyboard focusable, labels must remain visible, and focus styling must not be removed.</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Create reusable badge classes and one modifier class per state.</t>
+          <t>Set the correct positioning context for 'Create a Color Badge Set' before applying top/right/bottom/left or z-index values, then verify the layer appears exactly where the output page shows it.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Badge text must remain readable with sufficient contrast.</t>
+          <t>Do not change the provided HTML structure for 'Create a Color Badge Set'. The positioned element must stay inside or above the intended parent area and must not overlap unrelated content.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Set box-sizing globally and style the card class.</t>
+          <t>Inspect the provided markup for 'Apply the Box Model', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Cards must have equal width and visible borders.</t>
+          <t>Do not change the provided HTML structure for 'Apply the Box Model'. The submitted CSS must match the sample output for question 4 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Use input[type='text'], input[type='password'], and button selectors.</t>
+          <t>Style the form controls for 'Style a Login Form' in their normal and focus states; labels, inputs, helper text, and buttons should remain aligned and readable.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Do not use JavaScript. Keep fields full width inside the form.</t>
+          <t>Do not change the provided HTML structure for 'Style a Login Form'. Inputs must remain keyboard focusable, labels must remain visible, and focus styling must not be removed.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Use a gradient overlay and readable text color.</t>
+          <t>Inspect the provided markup for 'Add Background Effects', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>The heading must remain visible over the background.</t>
+          <t>Do not change the provided HTML structure for 'Add Background Effects'. The submitted CSS must match the sample output for question 6 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Remove list styles and style anchor hover states.</t>
+          <t>Inspect the provided markup for 'Build a Navigation Bar', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Nav links must have consistent spacing and no underline by default.</t>
+          <t>Do not change the provided HTML structure for 'Build a Navigation Bar'. The submitted CSS must match the sample output for question 7 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Use the ID for the featured tile and classes for shared styles.</t>
+          <t>Inspect the provided markup for 'Design a Product Tile', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Avoid using !important.</t>
+          <t>Do not change the provided HTML structure for 'Design a Product Tile'. The submitted CSS must match the sample output for question 8 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Apply a minimal reset before component styles.</t>
+          <t>Inspect the provided markup for 'Normalize Page Spacing', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Do not remove focus outlines.</t>
+          <t>Do not change the provided HTML structure for 'Normalize Page Spacing'. The submitted CSS must match the sample output for question 9 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Create one class per utility.</t>
+          <t>Focus on text hierarchy for 'Create Text Utility Classes': set font family, size, weight, line-height, spacing, and color to match the target output.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Each utility class must do one job only.</t>
+          <t>Do not change the provided HTML structure for 'Create Text Utility Classes'. Use rem or relative units for text sizing where appropriate; do not use viewport-width font sizing or clipped single-line text.</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Use element selectors and avoid inline styles.</t>
+          <t>Focus on text hierarchy for 'Style Heading Levels': set font family, size, weight, line-height, spacing, and color to match the target output.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Each heading level must look visually distinct.</t>
+          <t>Do not change the provided HTML structure for 'Style Heading Levels'. Use rem or relative units for text sizing where appropriate; do not use viewport-width font sizing or clipped single-line text.</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Use anchor pseudo-classes in a logical order.</t>
+          <t>Inspect the provided markup for 'Create Link Styles', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Do not remove keyboard focus visibility.</t>
+          <t>Do not change the provided HTML structure for 'Create Link Styles'. The submitted CSS must match the sample output for question 12 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Use one base alert class and modifier classes.</t>
+          <t>Choose foreground, background, and border colors for 'Build Alert Boxes' so every state is visually distinct and the text stays readable.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Each alert must include padding, border, and readable colors.</t>
+          <t>Do not change the provided HTML structure for 'Build Alert Boxes'. Each visual state must include readable text contrast and at least one non-color cue such as a border, label, icon, or spacing difference.</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Use font-family with multiple fallbacks.</t>
+          <t>Focus on text hierarchy for 'Use Font Families Correctly': set font family, size, weight, line-height, spacing, and color to match the target output.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Code text must use a monospace stack.</t>
+          <t>Do not change the provided HTML structure for 'Use Font Families Correctly'. Use rem or relative units for text sizing where appropriate; do not use viewport-width font sizing or clipped single-line text.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Use margin auto for horizontal centering.</t>
+          <t>Inspect the provided markup for 'Control Element Widths', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Container width must remain responsive.</t>
+          <t>Do not change the provided HTML structure for 'Control Element Widths'. The submitted CSS must match the sample output for question 15 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Use class selectors for each border type.</t>
+          <t>Inspect the provided markup for 'Add Border Variations', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Borders must not change the page layout unexpectedly.</t>
+          <t>Do not change the provided HTML structure for 'Add Border Variations'. The submitted CSS must match the sample output for question 16 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Use different radius values based on component shape.</t>
+          <t>Inspect the provided markup for 'Apply Rounded Corners', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Avatar must appear circular.</t>
+          <t>Do not change the provided HTML structure for 'Apply Rounded Corners'. The submitted CSS must match the sample output for question 17 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Use opacity only where it does not harm readability.</t>
+          <t>Inspect the provided markup for 'Practice Opacity', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Main text must remain fully readable.</t>
+          <t>Do not change the provided HTML structure for 'Practice Opacity'. The submitted CSS must match the sample output for question 18 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Group selectors that share the same declarations.</t>
+          <t>Inspect the provided markup for 'Group Shared Selectors', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Do not group selectors with different behavior.</t>
+          <t>Do not change the provided HTML structure for 'Group Shared Selectors'. The submitted CSS must match the sample output for question 19 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Keep each utility class focused on one property.</t>
+          <t>Inspect the provided markup for 'Create Simple Utility Classes', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Do not combine unrelated styles in one utility.</t>
+          <t>Do not change the provided HTML structure for 'Create Simple Utility Classes'. The submitted CSS must match the sample output for question 20 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Use justify-content and align-items on the navbar container.</t>
+          <t>Use Flexbox for 'Flex Navbar Alignment' and control alignment with justify-content, align-items, gap, flex-wrap, or flex-grow based on the target output.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Do not use floats. Keep the logo on the left and button on the right.</t>
+          <t>Do not change the provided HTML structure for 'Flex Navbar Alignment'. Use Flexbox for the main alignment; avoid floats, negative margins, and fixed pixel offsets for primary positioning.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Use flex-wrap and gap.</t>
+          <t>Start from the smallest screen layout for 'Responsive Card Row', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Cards must not overlap when the viewport is narrow.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Card Row'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Use grid-template-columns and align-items.</t>
+          <t>Inspect the provided markup for 'Two Column Portfolio Layout', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>At desktop width, text must appear before image.</t>
+          <t>Do not change the provided HTML structure for 'Two Column Portfolio Layout'. The submitted CSS must match the sample output for question 23 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Name grid areas clearly.</t>
+          <t>Use CSS Grid properties for 'Analytics Dashboard Grid', especially grid-template-columns, gap, and responsive track sizing where the target output shows structured rows or columns.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Sidebar must keep a fixed width on desktop.</t>
+          <t>Do not change the provided HTML structure for 'Analytics Dashboard Grid'. Use CSS Grid for the main arrangement; do not solve the layout with floats, HTML tables, or fixed absolute positions.</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Set the card to relative and the badge to absolute.</t>
+          <t>Set the correct positioning context for 'Absolute Badge Position' before applying top/right/bottom/left or z-index values, then verify the layer appears exactly where the output page shows it.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Badge must stay inside the card boundary.</t>
+          <t>Do not change the provided HTML structure for 'Absolute Badge Position'. The positioned element must stay inside or above the intended parent area and must not overlap unrelated content.</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Use position: sticky with a top offset.</t>
+          <t>Set the correct positioning context for 'Sticky Section Header' before applying top/right/bottom/left or z-index values, then verify the layer appears exactly where the output page shows it.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Toolbar must not cover the first row.</t>
+          <t>Do not change the provided HTML structure for 'Sticky Section Header'. Use position: sticky with an explicit top value; the sticky element must not hide the first content row.</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Use position: fixed and z-index.</t>
+          <t>Set the correct positioning context for 'Fixed Support Button' before applying top/right/bottom/left or z-index values, then verify the layer appears exactly where the output page shows it.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Button must remain visible above page content.</t>
+          <t>Do not change the provided HTML structure for 'Fixed Support Button'. Use position: fixed for the persistent action; it must remain visible above page content without blocking important text.</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Create separate overlay and modal layers.</t>
+          <t>Set the correct positioning context for 'Layered Modal Overlay' before applying top/right/bottom/left or z-index values, then verify the layer appears exactly where the output page shows it.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Modal must appear above overlay.</t>
+          <t>Do not change the provided HTML structure for 'Layered Modal Overlay'. The overlay must sit below the dialog, the dialog must remain visible above the overlay, and the page content must not visually cover the modal.</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Use repeat(auto-fit, minmax()).</t>
+          <t>Use CSS Grid properties for 'Grid Gallery Layout', especially grid-template-columns, gap, and responsive track sizing where the target output shows structured rows or columns.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Gallery items must keep equal gaps.</t>
+          <t>Do not change the provided HTML structure for 'Grid Gallery Layout'. Use CSS Grid for the main arrangement; do not solve the layout with floats, HTML tables, or fixed absolute positions.</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Use flex-basis or flex-grow for the input.</t>
+          <t>Use Flexbox for 'Flex Form Controls' and control alignment with justify-content, align-items, gap, flex-wrap, or flex-grow based on the target output.</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Input should take remaining width.</t>
+          <t>Do not change the provided HTML structure for 'Flex Form Controls'. Use Flexbox for the main alignment; avoid floats, negative margins, and fixed pixel offsets for primary positioning.</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Apply display flex to the parent container.</t>
+          <t>Use Flexbox for 'Center Content With Flexbox' and control alignment with justify-content, align-items, gap, flex-wrap, or flex-grow based on the target output.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Do not use absolute positioning.</t>
+          <t>Do not change the provided HTML structure for 'Center Content With Flexbox'. Use Flexbox for the main alignment; avoid floats, negative margins, and fixed pixel offsets for primary positioning.</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Use flex: 1 on child items.</t>
+          <t>Inspect the provided markup for 'Build Equal Width Columns', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Columns must keep equal width on desktop.</t>
+          <t>Do not change the provided HTML structure for 'Build Equal Width Columns'. The submitted CSS must match the sample output for question 32 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Use grid-template-columns and gap.</t>
+          <t>Use CSS Grid properties for 'Create a Simple Grid', especially grid-template-columns, gap, and responsive track sizing where the target output shows structured rows or columns.</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>No floats or table layout allowed.</t>
+          <t>Do not change the provided HTML structure for 'Create a Simple Grid'. Use CSS Grid for the main arrangement; do not solve the layout with floats, HTML tables, or fixed absolute positions.</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Use Flexbox alignment and gap.</t>
+          <t>Inspect the provided markup for 'Make a Header Layout', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Search box should take available space.</t>
+          <t>Do not change the provided HTML structure for 'Make a Header Layout'. The submitted CSS must match the sample output for question 34 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Set the notice container to position relative.</t>
+          <t>Set the correct positioning context for 'Position a Close Icon' before applying top/right/bottom/left or z-index values, then verify the layer appears exactly where the output page shows it.</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>The icon must remain inside the notice box.</t>
+          <t>Do not change the provided HTML structure for 'Position a Close Icon'. The positioned element must stay inside or above the intended parent area and must not overlap unrelated content.</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Use position sticky and top.</t>
+          <t>Use Flexbox for 'Create a Sticky Navbar' and control alignment with justify-content, align-items, gap, flex-wrap, or flex-grow based on the target output.</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Navbar must remain above page content.</t>
+          <t>Do not change the provided HTML structure for 'Create a Sticky Navbar'. Use Flexbox for the main alignment; avoid floats, negative margins, and fixed pixel offsets for primary positioning.</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Use gap instead of margin hacks.</t>
+          <t>Inspect the provided markup for 'Stack Cards With Gap', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Spacing between all cards must be equal.</t>
+          <t>Do not change the provided HTML structure for 'Stack Cards With Gap'. The submitted CSS must match the sample output for question 37 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Use grid-template-columns.</t>
+          <t>Use CSS Grid properties for 'Create Grid Sidebar Layout', especially grid-template-columns, gap, and responsive track sizing where the target output shows structured rows or columns.</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Sidebar must stay narrower than main content.</t>
+          <t>Do not change the provided HTML structure for 'Create Grid Sidebar Layout'. Use CSS Grid for the main arrangement; do not solve the layout with floats, HTML tables, or fixed absolute positions.</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Use positioned elements before z-index.</t>
+          <t>Set the correct positioning context for 'Control Z Index Layers' before applying top/right/bottom/left or z-index values, then verify the layer appears exactly where the output page shows it.</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Dropdown must appear above the page cards.</t>
+          <t>Do not change the provided HTML structure for 'Control Z Index Layers'. The positioned element must stay inside or above the intended parent area and must not overlap unrelated content.</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Use justify-content space-between.</t>
+          <t>Use Flexbox for 'Align Items in a Toolbar' and control alignment with justify-content, align-items, gap, flex-wrap, or flex-grow based on the target output.</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Toolbar items must remain vertically centered.</t>
+          <t>Do not change the provided HTML structure for 'Align Items in a Toolbar'. Use Flexbox for the main alignment; avoid floats, negative margins, and fixed pixel offsets for primary positioning.</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Write base mobile styles first, then add a media query.</t>
+          <t>Start from the smallest screen layout for 'Mobile First Navbar', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Use @media (min-width: 768px).</t>
+          <t>Do not change the provided HTML structure for 'Mobile First Navbar'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Use CSS Grid and media queries.</t>
+          <t>Start from the smallest screen layout for 'Responsive Card Grid', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Must start as one column on small screens.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Card Grid'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Use min-height and max-width constraints.</t>
+          <t>Inspect the provided markup for 'Fluid Hero Sizing', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Do not use fixed pixel widths for the main container.</t>
+          <t>Do not change the provided HTML structure for 'Fluid Hero Sizing'. The submitted CSS must match the sample output for question 43 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Use grid or flex with a breakpoint.</t>
+          <t>Start from the smallest screen layout for 'Responsive Form Layout', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Labels must stay above their fields.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Form Layout'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Define breakpoints for tablet and desktop.</t>
+          <t>Inspect the provided markup for 'Adaptive Dashboard Panels', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Widgets must preserve readable spacing.</t>
+          <t>Do not change the provided HTML structure for 'Adaptive Dashboard Panels'. The submitted CSS must match the sample output for question 45 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Use max-width, height:auto, and object-fit where needed.</t>
+          <t>Start from the smallest screen layout for 'Responsive Image Treatment', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Images must not overflow their containers.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Image Treatment'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Use vh carefully and override it in a media query.</t>
+          <t>Start from the smallest screen layout for 'Viewport Based Split Section', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Mobile content must not be clipped.</t>
+          <t>Do not change the provided HTML structure for 'Viewport Based Split Section'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Use CSS display changes inside a max-width media query.</t>
+          <t>Start from the smallest screen layout for 'Responsive Table Alternative', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Each mobile row must show label and value.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Table Alternative'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Define spacing variables on :root.</t>
+          <t>Inspect the provided markup for 'Scalable Spacing System', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Avoid hardcoding repeated pixel spacing.</t>
+          <t>Do not change the provided HTML structure for 'Scalable Spacing System'. The submitted CSS must match the sample output for question 49 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Use flex or grid with a breakpoint.</t>
+          <t>Start from the smallest screen layout for 'Accessible Responsive Footer', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Link tap targets must be at least 44px high on mobile.</t>
+          <t>Do not change the provided HTML structure for 'Accessible Responsive Footer'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Use @media (max-width: 600px).</t>
+          <t>Start from the smallest screen layout for 'Write Your First Media Query', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Mobile card must fit within the viewport.</t>
+          <t>Do not change the provided HTML structure for 'Write Your First Media Query'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Put mobile styles outside the media query.</t>
+          <t>Start from the smallest screen layout for 'Use Mobile First CSS', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Desktop rules must use min-width.</t>
+          <t>Do not change the provided HTML structure for 'Use Mobile First CSS'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Set body font size and paragraph max-width.</t>
+          <t>Start from the smallest screen layout for 'Make Text Responsive', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Do not use viewport-width font sizing.</t>
+          <t>Do not change the provided HTML structure for 'Make Text Responsive'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Use flex-direction and a breakpoint.</t>
+          <t>Start from the smallest screen layout for 'Responsive Button Group', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Buttons must remain easy to tap on mobile.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Button Group'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Use display none in a media query.</t>
+          <t>Start from the smallest screen layout for 'Hide Decorative Content on Mobile', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Do not hide important content.</t>
+          <t>Do not change the provided HTML structure for 'Hide Decorative Content on Mobile'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Use grid and a min-width breakpoint.</t>
+          <t>Start from the smallest screen layout for 'Responsive Pricing Cards', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Cards must not overflow on mobile.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Pricing Cards'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Use width 100% and height auto.</t>
+          <t>Inspect the provided markup for 'Fluid Image Banner', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Image must not appear stretched.</t>
+          <t>Do not change the provided HTML structure for 'Fluid Image Banner'. The submitted CSS must match the sample output for question 57 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Use CSS variables or media queries.</t>
+          <t>Start from the smallest screen layout for 'Responsive Spacing Tokens', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Mobile spacing must remain compact.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Spacing Tokens'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Use grid or flex with a breakpoint.</t>
+          <t>Start from the smallest screen layout for 'Responsive Sidebar Collapse', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Content must appear below navigation on mobile.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Sidebar Collapse'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Check fixed widths and use max-width.</t>
+          <t>Inspect the provided markup for 'Prevent Horizontal Scroll', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Page width must not exceed viewport width.</t>
+          <t>Do not change the provided HTML structure for 'Prevent Horizontal Scroll'. The submitted CSS must match the sample output for question 60 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Use spacing, text, border, and shadow utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Profile Card': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Do not write custom CSS.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Profile Card'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Use md:flex and gap utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Responsive Navbar': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Mobile layout must remain readable.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Responsive Navbar'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Use grid-cols-1, md:grid-cols-2, and lg:grid-cols-3.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Course Grid': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Cards must have equal spacing.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Course Grid'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Use hover:, focus:, and ring utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Button States': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Buttons must include visible focus styling.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Button States'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Apply classes directly to labels and inputs.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Form Panel': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Inputs must be full width.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Form Panel'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Use min-h-screen, w-64, and flex utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Sidebar Layout': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Sidebar should remain left aligned on desktop.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Sidebar Layout'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Assume the theme has brand colors configured.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Theme Color Usage': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Use brand utility names consistently.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Theme Color Usage'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Map spacing values to closest Tailwind scale.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Spacing System': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Do not use arbitrary values unless necessary.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Spacing System'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Use grid utilities and semantic text sizes.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Dashboard Widgets': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Widgets must align in a responsive grid.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Dashboard Widgets'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Use shared base classes and variant classes.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Production Component': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Each variant must have accessible contrast.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Production Component'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Use text, font, leading, and color utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Text Styling': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Do not write custom CSS.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Text Styling'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Use p, m, mt, and gap utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Spacing Practice': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>Avoid arbitrary values.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Spacing Practice'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Use min-h-screen, flex, items-center, and justify-center.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Flex Centering': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Do not use custom CSS.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Flex Centering'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Use rounded-full and px/py utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Color Badges': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>Badge colors must be readable.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Color Badges'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Use border, rounded, p, and shadow utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Border Card': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Card must have visible spacing.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Border Card'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Use text-2xl and md:text-4xl style classes.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Responsive Text': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>Base class must support mobile first.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Responsive Text'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Use grid, grid-cols-1, md:grid-cols-2, and gap.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Grid Basics': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>No custom media query allowed.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Grid Basics'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Use focus:ring and focus:border utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Form Inputs': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Focus state must be visible.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Form Inputs'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Use hover: utilities.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Button Hover': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Button text must remain readable on hover.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Button Hover'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Use utility classes only.</t>
+          <t>Use Tailwind utilities that directly express the target for 'Tailwind Simple Alert': spacing, color, layout, and state classes should be visible in the class attribute without adding a custom CSS file.</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Alert must include comfortable padding.</t>
+          <t>Do not change the provided HTML structure for 'Tailwind Simple Alert'. Use Tailwind utility classes only; do not add a separate CSS selector, inline style block, or arbitrary value unless the question explicitly requires it.</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Use transition and transform properties.</t>
+          <t>Implement the visible UI state for 'Hoverable Dashboard Card' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Hover effect must be subtle and not shift layout.</t>
+          <t>Do not change the provided HTML structure for 'Hoverable Dashboard Card'. The interaction effect must not resize surrounding layout or cause nearby text, buttons, or cards to jump.</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Use pseudo-classes and transitions.</t>
+          <t>Inspect the provided markup for 'Animated Submit Button', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Disabled state must look inactive and block pointer styling.</t>
+          <t>Do not change the provided HTML structure for 'Animated Submit Button'. The submitted CSS must match the sample output for question 82 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Use gradients and keyframe animation.</t>
+          <t>Implement the visible UI state for 'Skeleton Loading Card' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Animation should be smooth and not distract users.</t>
+          <t>Do not change the provided HTML structure for 'Skeleton Loading Card'. Animation duration should stay under 500ms for entrance effects, and layout-changing properties such as width, height, top, or left should be avoided.</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Use classes for active state and pseudo-classes for interactions.</t>
+          <t>Inspect the provided markup for 'Sidebar Navigation States', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>Active state must differ from hover state.</t>
+          <t>Do not change the provided HTML structure for 'Sidebar Navigation States'. The submitted CSS must match the sample output for question 84 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Use :focus, :valid, and :invalid selectors.</t>
+          <t>Style the form controls for 'Interactive Form Feedback' in their normal and focus states; labels, inputs, helper text, and buttons should remain aligned and readable.</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Invalid state must not rely only on color.</t>
+          <t>Do not change the provided HTML structure for 'Interactive Form Feedback'. Inputs must remain keyboard focusable, labels must remain visible, and focus styling must not be removed.</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Use heading, value, and helper text styles.</t>
+          <t>Inspect the provided markup for 'Card Widget Hierarchy', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>The metric value must be the most prominent element.</t>
+          <t>Do not change the provided HTML structure for 'Card Widget Hierarchy'. The submitted CSS must match the sample output for question 86 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Use @keyframes and animation properties.</t>
+          <t>Inspect the provided markup for 'Fade In Content Section', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Animation duration must be under 500ms.</t>
+          <t>Do not change the provided HTML structure for 'Fade In Content Section'. Animation duration should stay under 500ms for entrance effects, and layout-changing properties such as width, height, top, or left should be avoided.</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Use position and opacity transitions.</t>
+          <t>Inspect the provided markup for 'Accessible Tooltip Styling', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>Tooltip must work with keyboard focus.</t>
+          <t>Do not change the provided HTML structure for 'Accessible Tooltip Styling'. The submitted CSS must match the sample output for question 88 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Use transform, opacity, and transition.</t>
+          <t>Set the correct positioning context for 'Interactive Modal Motion' before applying top/right/bottom/left or z-index values, then verify the layer appears exactly where the output page shows it.</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Respect reduced motion with a media query.</t>
+          <t>Do not change the provided HTML structure for 'Interactive Modal Motion'. The overlay must sit below the dialog, the dialog must remain visible above the overlay, and the page content must not visually cover the modal.</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Use layout, spacing, and subtle color hierarchy.</t>
+          <t>Inspect the provided markup for 'Empty State Panel', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>The action button must remain visually prominent.</t>
+          <t>Do not change the provided HTML structure for 'Empty State Panel'. The submitted CSS must match the sample output for question 90 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Use transition on the button.</t>
+          <t>Implement the visible UI state for 'Button Hover Feedback' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Hover must not change button size.</t>
+          <t>Do not change the provided HTML structure for 'Button Hover Feedback'. The interaction effect must not resize surrounding layout or cause nearby text, buttons, or cards to jump.</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Use box-shadow and transition.</t>
+          <t>Implement the visible UI state for 'Card Hover Shadow' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>The card must not jump on hover.</t>
+          <t>Do not change the provided HTML structure for 'Card Hover Shadow'. The interaction effect must not resize surrounding layout or cause nearby text, buttons, or cards to jump.</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Use :focus and outline or box-shadow.</t>
+          <t>Style the form controls for 'Input Focus State' in their normal and focus states; labels, inputs, helper text, and buttons should remain aligned and readable.</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Do not remove focus feedback.</t>
+          <t>Do not change the provided HTML structure for 'Input Focus State'. Inputs must remain keyboard focusable, labels must remain visible, and focus styling must not be removed.</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Use opacity and cursor styles.</t>
+          <t>Implement the visible UI state for 'Simple Loading State' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>Button must look disabled.</t>
+          <t>Do not change the provided HTML structure for 'Simple Loading State'. Animation duration should stay under 500ms for entrance effects, and layout-changing properties such as width, height, top, or left should be avoided.</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Use an active class.</t>
+          <t>Implement the visible UI state for 'Create Active Menu Item' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Active state must be visually stronger than hover.</t>
+          <t>Do not change the provided HTML structure for 'Create Active Menu Item'. The submitted CSS must match the sample output for question 95 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Use @keyframes and animation.</t>
+          <t>Inspect the provided markup for 'Smooth Fade Effect', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>Animation must finish quickly.</t>
+          <t>Do not change the provided HTML structure for 'Smooth Fade Effect'. Animation duration should stay under 500ms for entrance effects, and layout-changing properties such as width, height, top, or left should be avoided.</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Use position absolute and opacity.</t>
+          <t>Inspect the provided markup for 'Icon Button Tooltip', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Tooltip text must be readable.</t>
+          <t>Do not change the provided HTML structure for 'Icon Button Tooltip'. The submitted CSS must match the sample output for question 97 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>Use spacing and visual hierarchy.</t>
+          <t>Inspect the provided markup for 'Design Empty State', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>Primary action must be easy to find.</t>
+          <t>Do not change the provided HTML structure for 'Design Empty State'. The submitted CSS must match the sample output for question 98 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Use color, spacing, and helper text.</t>
+          <t>Inspect the provided markup for 'Style Error Message', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Do not rely on color alone.</t>
+          <t>Do not change the provided HTML structure for 'Style Error Message'. The submitted CSS must match the sample output for question 99 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Use transition-property and duration.</t>
+          <t>Implement the visible UI state for 'Create Transitioned Panel' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>Effect must remain subtle.</t>
+          <t>Do not change the provided HTML structure for 'Create Transitioned Panel'. The interaction effect must not resize surrounding layout or cause nearby text, buttons, or cards to jump.</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Separate base class from variant classes.</t>
+          <t>Create reusable styling for 'Reusable Component Classes' by separating shared base rules from component-specific variants and using clear class names.</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Do not duplicate shared button declarations.</t>
+          <t>Do not change the provided HTML structure for 'Reusable Component Classes'. Class names must be predictable and reusable; do not rely on deeply nested selectors or remove semantic accessibility behavior.</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Use comments only for major sections.</t>
+          <t>Create reusable styling for 'Organized CSS Structure' by separating shared base rules from component-specific variants and using clear class names.</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>Keep selectors readable and avoid deep nesting.</t>
+          <t>Do not change the provided HTML structure for 'Organized CSS Structure'. Class names must be predictable and reusable; do not rely on deeply nested selectors or remove semantic accessibility behavior.</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>Define tokens on :root and override them with a theme class.</t>
+          <t>Create reusable styling for 'CSS Variables Theme' by separating shared base rules from component-specific variants and using clear class names.</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Components must use variables instead of hardcoded colors.</t>
+          <t>Do not change the provided HTML structure for 'CSS Variables Theme'. Repeated colors, spacing, or radius values must be represented with CSS custom properties and reused in component rules.</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>Choose foreground/background pairs with clear contrast.</t>
+          <t>Choose foreground, background, and border colors for 'Accessible Contrast Fix' so every state is visually distinct and the text stays readable.</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>Do not reduce font size to solve layout issues.</t>
+          <t>Do not change the provided HTML structure for 'Accessible Contrast Fix'. Each visual state must include readable text contrast and at least one non-color cue such as a border, label, icon, or spacing difference.</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Create predictable classes for each state.</t>
+          <t>Style the form controls for 'Production Form Component' in their normal and focus states; labels, inputs, helper text, and buttons should remain aligned and readable.</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Error text must be visible and associated with the field visually.</t>
+          <t>Do not change the provided HTML structure for 'Production Form Component'. Inputs must remain keyboard focusable, labels must remain visible, and focus styling must not be removed.</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>Prefer CSS gradients or optimized reusable assets.</t>
+          <t>Inspect the provided markup for 'Optimize CSS Asset Usage', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>Do not remove required brand visuals.</t>
+          <t>Do not change the provided HTML structure for 'Optimize CSS Asset Usage'. The submitted CSS must match the sample output for question 106 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Use a consistent prefix or BEM-style naming.</t>
+          <t>Create reusable styling for 'Component Scoped Naming' by separating shared base rules from component-specific variants and using clear class names.</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>Class names must communicate component ownership.</t>
+          <t>Do not change the provided HTML structure for 'Component Scoped Naming'. Class names must be predictable and reusable; do not rely on deeply nested selectors or remove semantic accessibility behavior.</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>Use reusable layout classes and responsive rules.</t>
+          <t>Inspect the provided markup for 'Production Dashboard Layout', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>The shell must remain usable on mobile.</t>
+          <t>Do not change the provided HTML structure for 'Production Dashboard Layout'. The submitted CSS must match the sample output for question 108 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Use semantic selectors carefully with classes for components.</t>
+          <t>Inspect the provided markup for 'Semantic UI Styling', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Do not remove outlines or hide labels.</t>
+          <t>Do not change the provided HTML structure for 'Semantic UI Styling'. Class names must be predictable and reusable; do not rely on deeply nested selectors or remove semantic accessibility behavior.</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>Animate transform and opacity only where possible.</t>
+          <t>Style the form controls for 'Performance Friendly Animation' in their normal and focus states; labels, inputs, helper text, and buttons should remain aligned and readable.</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>Avoid animating width, height, top, or left.</t>
+          <t>Do not change the provided HTML structure for 'Performance Friendly Animation'. Inputs must remain keyboard focusable, labels must remain visible, and focus styling must not be removed.</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>Use :root custom properties.</t>
+          <t>Create reusable styling for 'Create Design Tokens' by separating shared base rules from component-specific variants and using clear class names.</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Components must reference the variables.</t>
+          <t>Do not change the provided HTML structure for 'Create Design Tokens'. Repeated colors, spacing, or radius values must be represented with CSS custom properties and reused in component rules.</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>Use a shared base class and variants.</t>
+          <t>Create reusable styling for 'Reusable Button System' by separating shared base rules from component-specific variants and using clear class names.</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>Avoid duplicate declarations.</t>
+          <t>Do not change the provided HTML structure for 'Reusable Button System'. Class names must be predictable and reusable; do not rely on deeply nested selectors or remove semantic accessibility behavior.</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Use component-based class names.</t>
+          <t>Create reusable styling for 'Reusable Card Component' by separating shared base rules from component-specific variants and using clear class names.</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>Class names must be predictable.</t>
+          <t>Do not change the provided HTML structure for 'Reusable Card Component'. Class names must be predictable and reusable; do not rely on deeply nested selectors or remove semantic accessibility behavior.</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>Use :focus-visible.</t>
+          <t>Implement the visible UI state for 'Accessible Focus Styles' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>Do not set outline to none without replacement.</t>
+          <t>Do not change the provided HTML structure for 'Accessible Focus Styles'. The submitted CSS must match the sample output for question 114 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>Use short section comments.</t>
+          <t>Inspect the provided markup for 'Organize CSS File Sections', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Do not change behavior while organizing.</t>
+          <t>Do not change the provided HTML structure for 'Organize CSS File Sections'. The submitted CSS must match the sample output for question 115 without using JavaScript, external images, or !important.</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Use classes for component-specific styling.</t>
+          <t>Inspect the provided markup for 'Use Semantic Layout Classes', identify the key class names, and write the smallest set of CSS rules needed to reproduce the linked sample output.</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>Do not depend only on tag selectors.</t>
+          <t>Do not change the provided HTML structure for 'Use Semantic Layout Classes'. Class names must be predictable and reusable; do not rely on deeply nested selectors or remove semantic accessibility behavior.</t>
         </is>
       </c>
       <c r="I117" s="6" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>Create variables and reuse them.</t>
+          <t>Choose foreground, background, and border colors for 'Reduce Repeated Colors' so every state is visually distinct and the text stays readable.</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Keep the visual result unchanged.</t>
+          <t>Do not change the provided HTML structure for 'Reduce Repeated Colors'. Each visual state must include readable text contrast and at least one non-color cue such as a border, label, icon, or spacing difference.</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>Avoid animating layout properties.</t>
+          <t>Implement the visible UI state for 'Safe Animation Choices' with pseudo-classes, transitions, transforms, opacity, or keyframes while keeping the base state clear.</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>Do not animate width or height.</t>
+          <t>Do not change the provided HTML structure for 'Safe Animation Choices'. Animation duration should stay under 500ms for entrance effects, and layout-changing properties such as width, height, top, or left should be avoided.</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>Use a breakpoint to change layout.</t>
+          <t>Start from the smallest screen layout for 'Responsive Production Shell', then add the required breakpoint rule so the sample output changes layout without horizontal scrolling.</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Mobile layout must remain usable.</t>
+          <t>Do not change the provided HTML structure for 'Responsive Production Shell'. The final page must work at 375px and 1024px widths, must not create horizontal scroll, and must use the breakpoint behavior requested by the prompt.</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>Use icons, borders, or labels in addition to color.</t>
+          <t>Choose foreground, background, and border colors for 'Accessible Color States' so every state is visually distinct and the text stays readable.</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>Contrast must be readable.</t>
+          <t>Do not change the provided HTML structure for 'Accessible Color States'. Each visual state must include readable text contrast and at least one non-color cue such as a border, label, icon, or spacing difference.</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
